--- a/work/batch1/batch1-review.xlsx
+++ b/work/batch1/batch1-review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maost\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\[01] Martin\[07] Claude Code\NS2-Spanish-Translation\work\batch1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48995B67-6875-4F3C-9092-7EC9B47F6820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D638BC-65E1-42E0-9C79-7A6B76B80689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FE8904DB-09AE-4396-A75C-13F170AE1230}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{FE8904DB-09AE-4396-A75C-13F170AE1230}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3217" uniqueCount="1793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3806" uniqueCount="1816">
   <si>
     <t>Section</t>
   </si>
@@ -5422,6 +5422,75 @@
   </si>
   <si>
     <t>Flagged left</t>
+  </si>
+  <si>
+    <t>Use my Spanish</t>
+  </si>
+  <si>
+    <t>AVANZADAS</t>
+  </si>
+  <si>
+    <t>means options</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>FONDO DEL MENÚ</t>
+  </si>
+  <si>
+    <t>IR AL READY ROOM</t>
+  </si>
+  <si>
+    <t>MÚSICA DEL MENÚ</t>
+  </si>
+  <si>
+    <t>PARTIDAS ORGANIZADAS</t>
+  </si>
+  <si>
+    <t>SERVIDORES COMUNITARIOS</t>
+  </si>
+  <si>
+    <t>Explorar el Workshop de Steam</t>
+  </si>
+  <si>
+    <t>Ver mods en el Workshop de Steam (no se puede abrir durante la partida: la interfaz de Steam en el juego está desactivada)</t>
+  </si>
+  <si>
+    <t>Ser espectador</t>
+  </si>
+  <si>
+    <t>ENTRENAMIENTO BÁSICO</t>
+  </si>
+  <si>
+    <t>Este es un servidor de entrenamiento básico. Tienes demasiada experiencia para jugar aquí.</t>
+  </si>
+  <si>
+    <t>JUGAR IGUALMENTE</t>
+  </si>
+  <si>
+    <t>Keep current</t>
+  </si>
+  <si>
+    <t>DURACIÒN DE TEXTURAS DE IMPACTOS</t>
+  </si>
+  <si>
+    <t>Borrar asignación</t>
+  </si>
+  <si>
+    <t>OPACIDAD DE LOS NOMBRES DE LOS CUARTOS</t>
+  </si>
+  <si>
+    <t>Define la transparencia de los nombres de los cuartos en el mapa.</t>
+  </si>
+  <si>
+    <t>Activa o desactiva el efecto de balas trazadoras de las armas.</t>
+  </si>
+  <si>
+    <t>Activa la habilidad de movimiento especial de la forma de vida actual. Para los Marines es correr; para los Skulks, moverse sigilosamente, etc.</t>
+  </si>
+  <si>
+    <t>RESTABLECER TECLAS DE CUADRÍCULA</t>
   </si>
 </sst>
 </file>
@@ -5982,7 +6051,7 @@
       </c>
       <c r="B10" s="14">
         <f>COUNTA(Review!J2:J568)</f>
-        <v>0</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -5991,7 +6060,7 @@
       </c>
       <c r="B11" s="14">
         <f>ROWS(Review!J2:J568)-COUNTA(Review!J2:J568)</f>
-        <v>567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -6000,7 +6069,7 @@
       </c>
       <c r="B12" s="14">
         <f>COUNTIFS(Review!G2:G568,"?*",Review!J2:J568,"")</f>
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6027,7 +6096,7 @@
     <col min="12" max="12" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6085,9 +6154,15 @@
       <c r="G2" s="3"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="J2" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>1795</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -6111,7 +6186,9 @@
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="6"/>
+      <c r="J3" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
@@ -6137,8 +6214,12 @@
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
+      <c r="J4" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>1797</v>
+      </c>
       <c r="L4" s="7"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -6161,7 +6242,9 @@
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="6"/>
+      <c r="J5" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
@@ -6185,7 +6268,9 @@
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="6"/>
+      <c r="J6" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
@@ -6211,7 +6296,9 @@
         <v>32</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
     </row>
@@ -6237,7 +6324,9 @@
         <v>35</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="6"/>
+      <c r="J8" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
@@ -6263,7 +6352,9 @@
         <v>35</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="6"/>
+      <c r="J9" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
@@ -6289,7 +6380,9 @@
         <v>35</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
@@ -6315,7 +6408,9 @@
         <v>35</v>
       </c>
       <c r="I11" s="4"/>
-      <c r="J11" s="6"/>
+      <c r="J11" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
@@ -6341,7 +6436,9 @@
         <v>35</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="J12" s="6"/>
+      <c r="J12" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
@@ -6367,7 +6464,9 @@
         <v>35</v>
       </c>
       <c r="I13" s="4"/>
-      <c r="J13" s="6"/>
+      <c r="J13" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
@@ -6393,7 +6492,9 @@
         <v>35</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="6"/>
+      <c r="J14" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
@@ -6419,7 +6520,9 @@
         <v>35</v>
       </c>
       <c r="I15" s="4"/>
-      <c r="J15" s="6"/>
+      <c r="J15" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
     </row>
@@ -6445,7 +6548,9 @@
         <v>35</v>
       </c>
       <c r="I16" s="4"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
     </row>
@@ -6471,7 +6576,9 @@
         <v>35</v>
       </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="6"/>
+      <c r="J17" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
     </row>
@@ -6497,7 +6604,9 @@
         <v>35</v>
       </c>
       <c r="I18" s="4"/>
-      <c r="J18" s="6"/>
+      <c r="J18" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
     </row>
@@ -6523,7 +6632,9 @@
         <v>35</v>
       </c>
       <c r="I19" s="4"/>
-      <c r="J19" s="6"/>
+      <c r="J19" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
     </row>
@@ -6549,7 +6660,9 @@
         <v>35</v>
       </c>
       <c r="I20" s="4"/>
-      <c r="J20" s="6"/>
+      <c r="J20" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
@@ -6575,7 +6688,9 @@
         <v>35</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="6"/>
+      <c r="J21" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
@@ -6601,7 +6716,9 @@
         <v>35</v>
       </c>
       <c r="I22" s="4"/>
-      <c r="J22" s="6"/>
+      <c r="J22" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
@@ -6625,7 +6742,9 @@
       <c r="G23" s="3"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="6"/>
+      <c r="J23" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
     </row>
@@ -6651,7 +6770,9 @@
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="6"/>
+      <c r="J24" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
@@ -6677,7 +6798,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="6"/>
+      <c r="J25" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
@@ -6703,7 +6826,9 @@
       <c r="G26" s="3"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="6"/>
+      <c r="J26" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
@@ -6729,7 +6854,9 @@
       <c r="G27" s="3"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="6"/>
+      <c r="J27" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
     </row>
@@ -6755,7 +6882,9 @@
       <c r="G28" s="3"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="6"/>
+      <c r="J28" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
@@ -6785,7 +6914,9 @@
       <c r="I29" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="6"/>
+      <c r="J29" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
@@ -6811,7 +6942,9 @@
       <c r="G30" s="3"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="6"/>
+      <c r="J30" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
@@ -6837,7 +6970,9 @@
         <v>93</v>
       </c>
       <c r="I31" s="4"/>
-      <c r="J31" s="6"/>
+      <c r="J31" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
@@ -6863,8 +6998,12 @@
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="7"/>
+      <c r="J32" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>1798</v>
+      </c>
       <c r="L32" s="7"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -6887,7 +7026,9 @@
       <c r="G33" s="3"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="6"/>
+      <c r="J33" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
@@ -6911,7 +7052,9 @@
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="6"/>
+      <c r="J34" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
@@ -6939,7 +7082,9 @@
         <v>106</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="6"/>
+      <c r="J35" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
     </row>
@@ -6965,7 +7110,9 @@
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="6"/>
+      <c r="J36" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
     </row>
@@ -6991,7 +7138,9 @@
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="6"/>
+      <c r="J37" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
     </row>
@@ -7015,7 +7164,9 @@
       <c r="G38" s="3"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="6"/>
+      <c r="J38" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
     </row>
@@ -7039,7 +7190,9 @@
       <c r="G39" s="3"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="6"/>
+      <c r="J39" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
@@ -7063,7 +7216,9 @@
       <c r="G40" s="3"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="6"/>
+      <c r="J40" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
@@ -7089,8 +7244,12 @@
       <c r="G41" s="3"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="7"/>
+      <c r="J41" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>1799</v>
+      </c>
       <c r="L41" s="7"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -7113,7 +7272,9 @@
       <c r="G42" s="3"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="6"/>
+      <c r="J42" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
     </row>
@@ -7137,7 +7298,9 @@
       <c r="G43" s="3"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="6"/>
+      <c r="J43" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
     </row>
@@ -7163,7 +7326,9 @@
         <v>132</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="J44" s="6"/>
+      <c r="J44" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
@@ -7189,7 +7354,9 @@
         <v>132</v>
       </c>
       <c r="I45" s="4"/>
-      <c r="J45" s="6"/>
+      <c r="J45" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
     </row>
@@ -7215,7 +7382,9 @@
         <v>132</v>
       </c>
       <c r="I46" s="4"/>
-      <c r="J46" s="6"/>
+      <c r="J46" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
@@ -7241,7 +7410,9 @@
         <v>132</v>
       </c>
       <c r="I47" s="4"/>
-      <c r="J47" s="6"/>
+      <c r="J47" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
@@ -7267,7 +7438,9 @@
         <v>132</v>
       </c>
       <c r="I48" s="4"/>
-      <c r="J48" s="6"/>
+      <c r="J48" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
@@ -7293,7 +7466,9 @@
       <c r="G49" s="3"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="6"/>
+      <c r="J49" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
     </row>
@@ -7323,8 +7498,12 @@
         <v>147</v>
       </c>
       <c r="I50" s="4"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="7"/>
+      <c r="J50" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>1800</v>
+      </c>
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
@@ -7347,7 +7526,9 @@
       <c r="G51" s="3"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="6"/>
+      <c r="J51" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
     </row>
@@ -7373,7 +7554,9 @@
       <c r="G52" s="3"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="6"/>
+      <c r="J52" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
     </row>
@@ -7403,8 +7586,12 @@
         <v>160</v>
       </c>
       <c r="I53" s="4"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="7"/>
+      <c r="J53" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="L53" s="7"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -7427,7 +7614,9 @@
       <c r="G54" s="3"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="6"/>
+      <c r="J54" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
@@ -7455,7 +7644,9 @@
         <v>167</v>
       </c>
       <c r="I55" s="4"/>
-      <c r="J55" s="6"/>
+      <c r="J55" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
     </row>
@@ -7481,7 +7672,9 @@
       <c r="G56" s="3"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="6"/>
+      <c r="J56" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
     </row>
@@ -7507,7 +7700,9 @@
       <c r="G57" s="3"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="6"/>
+      <c r="J57" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
     </row>
@@ -7533,7 +7728,9 @@
         <v>177</v>
       </c>
       <c r="I58" s="4"/>
-      <c r="J58" s="6"/>
+      <c r="J58" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
@@ -7563,8 +7760,12 @@
         <v>182</v>
       </c>
       <c r="I59" s="4"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="7"/>
+      <c r="J59" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>1801</v>
+      </c>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -7593,7 +7794,9 @@
         <v>187</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="J60" s="6"/>
+      <c r="J60" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
     </row>
@@ -7617,7 +7820,9 @@
       <c r="G61" s="3"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="6"/>
+      <c r="J61" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
     </row>
@@ -7643,7 +7848,9 @@
       <c r="G62" s="3"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="6"/>
+      <c r="J62" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
     </row>
@@ -7673,7 +7880,9 @@
         <v>198</v>
       </c>
       <c r="I63" s="4"/>
-      <c r="J63" s="6"/>
+      <c r="J63" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
     </row>
@@ -7699,7 +7908,9 @@
       <c r="G64" s="3"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="6"/>
+      <c r="J64" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
     </row>
@@ -7725,7 +7936,9 @@
         <v>204</v>
       </c>
       <c r="I65" s="4"/>
-      <c r="J65" s="6"/>
+      <c r="J65" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
     </row>
@@ -7749,8 +7962,12 @@
       <c r="G66" s="3"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="7"/>
+      <c r="J66" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>1802</v>
+      </c>
       <c r="L66" s="7"/>
     </row>
     <row r="67" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
@@ -7775,8 +7992,12 @@
         <v>211</v>
       </c>
       <c r="I67" s="4"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="7"/>
+      <c r="J67" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>1803</v>
+      </c>
       <c r="L67" s="7"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -7799,7 +8020,9 @@
       <c r="G68" s="3"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="6"/>
+      <c r="J68" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
     </row>
@@ -7823,7 +8046,9 @@
       <c r="G69" s="3"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="6"/>
+      <c r="J69" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
@@ -7847,7 +8072,9 @@
       <c r="G70" s="3"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="6"/>
+      <c r="J70" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
     </row>
@@ -7877,7 +8104,9 @@
         <v>222</v>
       </c>
       <c r="I71" s="4"/>
-      <c r="J71" s="6"/>
+      <c r="J71" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
     </row>
@@ -7901,7 +8130,9 @@
       <c r="G72" s="3"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="6"/>
+      <c r="J72" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
     </row>
@@ -7927,7 +8158,9 @@
       <c r="G73" s="3"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="6"/>
+      <c r="J73" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
     </row>
@@ -7953,8 +8186,12 @@
         <v>232</v>
       </c>
       <c r="I74" s="4"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="7"/>
+      <c r="J74" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>1806</v>
+      </c>
       <c r="L74" s="7"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -7977,7 +8214,9 @@
       <c r="G75" s="3"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="6"/>
+      <c r="J75" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
     </row>
@@ -8001,7 +8240,9 @@
       <c r="G76" s="3"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="6"/>
+      <c r="J76" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
     </row>
@@ -8029,8 +8270,12 @@
         <v>242</v>
       </c>
       <c r="I77" s="4"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="7"/>
+      <c r="J77" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>1804</v>
+      </c>
       <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
@@ -8057,8 +8302,12 @@
         <v>245</v>
       </c>
       <c r="I78" s="4"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="7"/>
+      <c r="J78" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>1805</v>
+      </c>
       <c r="L78" s="7"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -8081,7 +8330,9 @@
       <c r="G79" s="3"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="6"/>
+      <c r="J79" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
@@ -8105,7 +8356,9 @@
       <c r="G80" s="3"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="6"/>
+      <c r="J80" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
     </row>
@@ -8129,7 +8382,9 @@
       <c r="G81" s="3"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="6"/>
+      <c r="J81" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
     </row>
@@ -8153,7 +8408,9 @@
       <c r="G82" s="3"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="6"/>
+      <c r="J82" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
     </row>
@@ -8177,7 +8434,9 @@
       <c r="G83" s="3"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="6"/>
+      <c r="J83" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
     </row>
@@ -8203,7 +8462,9 @@
         <v>262</v>
       </c>
       <c r="I84" s="4"/>
-      <c r="J84" s="6"/>
+      <c r="J84" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
     </row>
@@ -8227,7 +8488,9 @@
       <c r="G85" s="3"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
-      <c r="J85" s="6"/>
+      <c r="J85" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
     </row>
@@ -8255,7 +8518,9 @@
         <v>269</v>
       </c>
       <c r="I86" s="4"/>
-      <c r="J86" s="6"/>
+      <c r="J86" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
     </row>
@@ -8283,7 +8548,9 @@
         <v>273</v>
       </c>
       <c r="I87" s="4"/>
-      <c r="J87" s="6"/>
+      <c r="J87" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
     </row>
@@ -8307,7 +8574,9 @@
       <c r="G88" s="3"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="6"/>
+      <c r="J88" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
     </row>
@@ -8331,7 +8600,9 @@
       <c r="G89" s="3"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="J89" s="6"/>
+      <c r="J89" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
     </row>
@@ -8355,7 +8626,9 @@
       <c r="G90" s="3"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
-      <c r="J90" s="6"/>
+      <c r="J90" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
     </row>
@@ -8381,7 +8654,9 @@
       <c r="G91" s="3"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="6"/>
+      <c r="J91" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
@@ -8407,7 +8682,9 @@
       <c r="G92" s="3"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="6"/>
+      <c r="J92" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
@@ -8431,7 +8708,9 @@
       <c r="G93" s="3"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="6"/>
+      <c r="J93" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
@@ -8457,7 +8736,9 @@
       <c r="G94" s="3"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="6"/>
+      <c r="J94" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
@@ -8483,8 +8764,12 @@
       <c r="I95" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J95" s="6"/>
-      <c r="K95" s="7"/>
+      <c r="J95" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>1807</v>
+      </c>
       <c r="L95" s="7"/>
     </row>
     <row r="96" spans="1:12" ht="76.5" x14ac:dyDescent="0.2">
@@ -8511,7 +8796,9 @@
         <v>300</v>
       </c>
       <c r="I96" s="4"/>
-      <c r="J96" s="6"/>
+      <c r="J96" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
     </row>
@@ -8535,7 +8822,9 @@
       <c r="G97" s="3"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="6"/>
+      <c r="J97" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
     </row>
@@ -8559,7 +8848,9 @@
       <c r="G98" s="3"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="6"/>
+      <c r="J98" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
     </row>
@@ -8585,7 +8876,9 @@
         <v>310</v>
       </c>
       <c r="I99" s="4"/>
-      <c r="J99" s="6"/>
+      <c r="J99" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
     </row>
@@ -8609,7 +8902,9 @@
       <c r="G100" s="3"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="6"/>
+      <c r="J100" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
     </row>
@@ -8633,7 +8928,9 @@
       <c r="G101" s="3"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="6"/>
+      <c r="J101" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
     </row>
@@ -8657,7 +8954,9 @@
       <c r="G102" s="3"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="6"/>
+      <c r="J102" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
     </row>
@@ -8685,7 +8984,9 @@
         <v>323</v>
       </c>
       <c r="I103" s="4"/>
-      <c r="J103" s="6"/>
+      <c r="J103" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
     </row>
@@ -8709,7 +9010,9 @@
       <c r="G104" s="3"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="6"/>
+      <c r="J104" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
     </row>
@@ -8733,7 +9036,9 @@
       <c r="G105" s="3"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="6"/>
+      <c r="J105" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
     </row>
@@ -8757,7 +9062,9 @@
       <c r="G106" s="3"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="6"/>
+      <c r="J106" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
     </row>
@@ -8781,7 +9088,9 @@
       <c r="G107" s="3"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
-      <c r="J107" s="6"/>
+      <c r="J107" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
     </row>
@@ -8805,7 +9114,9 @@
       <c r="G108" s="3"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="6"/>
+      <c r="J108" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
     </row>
@@ -8829,7 +9140,9 @@
       <c r="G109" s="3"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-      <c r="J109" s="6"/>
+      <c r="J109" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
     </row>
@@ -8853,7 +9166,9 @@
       <c r="G110" s="3"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
-      <c r="J110" s="6"/>
+      <c r="J110" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
     </row>
@@ -8879,7 +9194,9 @@
       <c r="G111" s="3"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-      <c r="J111" s="6"/>
+      <c r="J111" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
     </row>
@@ -8905,7 +9222,9 @@
       <c r="G112" s="3"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="6"/>
+      <c r="J112" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
     </row>
@@ -8931,7 +9250,9 @@
       <c r="G113" s="3"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-      <c r="J113" s="6"/>
+      <c r="J113" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
     </row>
@@ -8955,7 +9276,9 @@
       <c r="G114" s="3"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="J114" s="6"/>
+      <c r="J114" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
     </row>
@@ -8979,7 +9302,9 @@
       <c r="G115" s="3"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-      <c r="J115" s="6"/>
+      <c r="J115" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
     </row>
@@ -9005,7 +9330,9 @@
       <c r="G116" s="3"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
-      <c r="J116" s="6"/>
+      <c r="J116" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
     </row>
@@ -9035,7 +9362,9 @@
         <v>367</v>
       </c>
       <c r="I117" s="4"/>
-      <c r="J117" s="6"/>
+      <c r="J117" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
     </row>
@@ -9061,7 +9390,9 @@
       <c r="G118" s="3"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="6"/>
+      <c r="J118" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
     </row>
@@ -9087,7 +9418,9 @@
         <v>375</v>
       </c>
       <c r="I119" s="4"/>
-      <c r="J119" s="6"/>
+      <c r="J119" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
     </row>
@@ -9111,7 +9444,9 @@
       <c r="G120" s="3"/>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
-      <c r="J120" s="6"/>
+      <c r="J120" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
     </row>
@@ -9137,7 +9472,9 @@
       <c r="G121" s="3"/>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
-      <c r="J121" s="6"/>
+      <c r="J121" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
     </row>
@@ -9161,7 +9498,9 @@
       <c r="G122" s="3"/>
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
-      <c r="J122" s="6"/>
+      <c r="J122" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
     </row>
@@ -9185,7 +9524,9 @@
       <c r="G123" s="3"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
-      <c r="J123" s="6"/>
+      <c r="J123" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
     </row>
@@ -9209,7 +9550,9 @@
       <c r="G124" s="3"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
-      <c r="J124" s="6"/>
+      <c r="J124" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
     </row>
@@ -9235,7 +9578,9 @@
       <c r="G125" s="3"/>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
-      <c r="J125" s="6"/>
+      <c r="J125" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
     </row>
@@ -9261,7 +9606,9 @@
       <c r="G126" s="3"/>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
-      <c r="J126" s="6"/>
+      <c r="J126" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
     </row>
@@ -9285,7 +9632,9 @@
       <c r="G127" s="3"/>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
-      <c r="J127" s="6"/>
+      <c r="J127" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
     </row>
@@ -9315,7 +9664,9 @@
         <v>403</v>
       </c>
       <c r="I128" s="4"/>
-      <c r="J128" s="6"/>
+      <c r="J128" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
     </row>
@@ -9339,7 +9690,9 @@
       <c r="G129" s="3"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
-      <c r="J129" s="6"/>
+      <c r="J129" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
     </row>
@@ -9363,7 +9716,9 @@
       <c r="G130" s="3"/>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
-      <c r="J130" s="6"/>
+      <c r="J130" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
     </row>
@@ -9391,7 +9746,9 @@
         <v>413</v>
       </c>
       <c r="I131" s="4"/>
-      <c r="J131" s="6"/>
+      <c r="J131" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
     </row>
@@ -9417,7 +9774,9 @@
       <c r="G132" s="3"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
-      <c r="J132" s="6"/>
+      <c r="J132" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
     </row>
@@ -9443,7 +9802,9 @@
         <v>417</v>
       </c>
       <c r="I133" s="4"/>
-      <c r="J133" s="6"/>
+      <c r="J133" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
     </row>
@@ -9467,7 +9828,9 @@
       <c r="G134" s="3"/>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
-      <c r="J134" s="6"/>
+      <c r="J134" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
     </row>
@@ -9493,7 +9856,9 @@
         <v>424</v>
       </c>
       <c r="I135" s="4"/>
-      <c r="J135" s="6"/>
+      <c r="J135" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
     </row>
@@ -9523,7 +9888,9 @@
         <v>429</v>
       </c>
       <c r="I136" s="4"/>
-      <c r="J136" s="6"/>
+      <c r="J136" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
     </row>
@@ -9553,7 +9920,9 @@
         <v>434</v>
       </c>
       <c r="I137" s="4"/>
-      <c r="J137" s="6"/>
+      <c r="J137" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
     </row>
@@ -9583,7 +9952,9 @@
         <v>434</v>
       </c>
       <c r="I138" s="4"/>
-      <c r="J138" s="6"/>
+      <c r="J138" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
     </row>
@@ -9613,7 +9984,9 @@
         <v>434</v>
       </c>
       <c r="I139" s="4"/>
-      <c r="J139" s="6"/>
+      <c r="J139" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
     </row>
@@ -9637,7 +10010,9 @@
       <c r="G140" s="3"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
-      <c r="J140" s="6"/>
+      <c r="J140" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
     </row>
@@ -9661,7 +10036,9 @@
       <c r="G141" s="3"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
-      <c r="J141" s="6"/>
+      <c r="J141" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
     </row>
@@ -9685,7 +10062,9 @@
       <c r="G142" s="3"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
-      <c r="J142" s="6"/>
+      <c r="J142" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
     </row>
@@ -9709,7 +10088,9 @@
       <c r="G143" s="3"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
-      <c r="J143" s="6"/>
+      <c r="J143" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
     </row>
@@ -9739,8 +10120,12 @@
         <v>458</v>
       </c>
       <c r="I144" s="4"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="7"/>
+      <c r="J144" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K144" s="7" t="s">
+        <v>1809</v>
+      </c>
       <c r="L144" s="7"/>
     </row>
     <row r="145" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
@@ -9763,7 +10148,9 @@
       <c r="G145" s="3"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
-      <c r="J145" s="6"/>
+      <c r="J145" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
     </row>
@@ -9787,7 +10174,9 @@
       <c r="G146" s="3"/>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
-      <c r="J146" s="6"/>
+      <c r="J146" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
     </row>
@@ -9813,7 +10202,9 @@
       <c r="G147" s="3"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
-      <c r="J147" s="6"/>
+      <c r="J147" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
     </row>
@@ -9839,7 +10230,9 @@
       <c r="G148" s="3"/>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
-      <c r="J148" s="6"/>
+      <c r="J148" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
     </row>
@@ -9865,7 +10258,9 @@
       <c r="G149" s="3"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
-      <c r="J149" s="6"/>
+      <c r="J149" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
     </row>
@@ -9895,7 +10290,9 @@
         <v>475</v>
       </c>
       <c r="I150" s="4"/>
-      <c r="J150" s="6"/>
+      <c r="J150" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
     </row>
@@ -9919,7 +10316,9 @@
       <c r="G151" s="3"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
-      <c r="J151" s="6"/>
+      <c r="J151" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
     </row>
@@ -9943,7 +10342,9 @@
       <c r="G152" s="3"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
-      <c r="J152" s="6"/>
+      <c r="J152" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
     </row>
@@ -9967,7 +10368,9 @@
       <c r="G153" s="3"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
-      <c r="J153" s="6"/>
+      <c r="J153" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
     </row>
@@ -9991,7 +10394,9 @@
       <c r="G154" s="3"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
-      <c r="J154" s="6"/>
+      <c r="J154" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
     </row>
@@ -10015,7 +10420,9 @@
       <c r="G155" s="3"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
-      <c r="J155" s="6"/>
+      <c r="J155" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
     </row>
@@ -10043,7 +10450,9 @@
       <c r="I156" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="J156" s="6"/>
+      <c r="J156" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
     </row>
@@ -10067,7 +10476,9 @@
       <c r="G157" s="3"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
-      <c r="J157" s="6"/>
+      <c r="J157" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
     </row>
@@ -10097,7 +10508,9 @@
         <v>500</v>
       </c>
       <c r="I158" s="4"/>
-      <c r="J158" s="6"/>
+      <c r="J158" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
     </row>
@@ -10121,7 +10534,9 @@
       <c r="G159" s="3"/>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
-      <c r="J159" s="6"/>
+      <c r="J159" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
     </row>
@@ -10145,7 +10560,9 @@
       <c r="G160" s="3"/>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
-      <c r="J160" s="6"/>
+      <c r="J160" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
     </row>
@@ -10171,7 +10588,9 @@
       <c r="G161" s="3"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
-      <c r="J161" s="6"/>
+      <c r="J161" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
     </row>
@@ -10195,7 +10614,9 @@
       <c r="G162" s="3"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
-      <c r="J162" s="6"/>
+      <c r="J162" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
     </row>
@@ -10221,7 +10642,9 @@
       <c r="G163" s="3"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
-      <c r="J163" s="6"/>
+      <c r="J163" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
     </row>
@@ -10253,7 +10676,9 @@
       <c r="I164" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="J164" s="6"/>
+      <c r="J164" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
     </row>
@@ -10279,7 +10704,9 @@
       <c r="I165" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="J165" s="6"/>
+      <c r="J165" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
     </row>
@@ -10303,7 +10730,9 @@
       <c r="G166" s="3"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
-      <c r="J166" s="6"/>
+      <c r="J166" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
     </row>
@@ -10331,7 +10760,9 @@
       <c r="I167" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="J167" s="6"/>
+      <c r="J167" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
     </row>
@@ -10355,7 +10786,9 @@
       <c r="G168" s="3"/>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
-      <c r="J168" s="6"/>
+      <c r="J168" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
     </row>
@@ -10379,7 +10812,9 @@
       <c r="G169" s="3"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
-      <c r="J169" s="6"/>
+      <c r="J169" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
     </row>
@@ -10407,7 +10842,9 @@
       <c r="I170" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="J170" s="6"/>
+      <c r="J170" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
     </row>
@@ -10431,7 +10868,9 @@
       <c r="G171" s="3"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
-      <c r="J171" s="6"/>
+      <c r="J171" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
     </row>
@@ -10457,7 +10896,9 @@
         <v>545</v>
       </c>
       <c r="I172" s="4"/>
-      <c r="J172" s="6"/>
+      <c r="J172" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
     </row>
@@ -10483,7 +10924,9 @@
       <c r="G173" s="3"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
-      <c r="J173" s="6"/>
+      <c r="J173" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
     </row>
@@ -10509,7 +10952,9 @@
       <c r="G174" s="3"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
-      <c r="J174" s="6"/>
+      <c r="J174" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
     </row>
@@ -10535,7 +10980,9 @@
       <c r="G175" s="3"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
-      <c r="J175" s="6"/>
+      <c r="J175" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
     </row>
@@ -10559,7 +11006,9 @@
       <c r="G176" s="3"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
-      <c r="J176" s="6"/>
+      <c r="J176" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
     </row>
@@ -10583,7 +11032,9 @@
       <c r="G177" s="3"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
-      <c r="J177" s="6"/>
+      <c r="J177" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
     </row>
@@ -10607,7 +11058,9 @@
       <c r="G178" s="3"/>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
-      <c r="J178" s="6"/>
+      <c r="J178" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
     </row>
@@ -10633,7 +11086,9 @@
       <c r="G179" s="3"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
-      <c r="J179" s="6"/>
+      <c r="J179" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
     </row>
@@ -10659,7 +11114,9 @@
       <c r="G180" s="3"/>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
-      <c r="J180" s="6"/>
+      <c r="J180" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
     </row>
@@ -10685,7 +11142,9 @@
       <c r="G181" s="3"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
-      <c r="J181" s="6"/>
+      <c r="J181" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
     </row>
@@ -10715,7 +11174,9 @@
         <v>574</v>
       </c>
       <c r="I182" s="4"/>
-      <c r="J182" s="6"/>
+      <c r="J182" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
     </row>
@@ -10739,7 +11200,9 @@
       <c r="G183" s="3"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
-      <c r="J183" s="6"/>
+      <c r="J183" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
     </row>
@@ -10769,7 +11232,9 @@
         <v>581</v>
       </c>
       <c r="I184" s="4"/>
-      <c r="J184" s="6"/>
+      <c r="J184" s="6" t="s">
+        <v>1808</v>
+      </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
     </row>
@@ -10795,7 +11260,9 @@
       <c r="G185" s="3"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
-      <c r="J185" s="6"/>
+      <c r="J185" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
     </row>
@@ -10819,7 +11286,9 @@
       <c r="G186" s="3"/>
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
-      <c r="J186" s="6"/>
+      <c r="J186" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
     </row>
@@ -10843,7 +11312,9 @@
       <c r="G187" s="3"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
-      <c r="J187" s="6"/>
+      <c r="J187" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
     </row>
@@ -10873,7 +11344,9 @@
         <v>594</v>
       </c>
       <c r="I188" s="4"/>
-      <c r="J188" s="6"/>
+      <c r="J188" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
     </row>
@@ -10897,7 +11370,9 @@
       <c r="G189" s="3"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
-      <c r="J189" s="6"/>
+      <c r="J189" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
     </row>
@@ -10927,7 +11402,9 @@
         <v>602</v>
       </c>
       <c r="I190" s="4"/>
-      <c r="J190" s="6"/>
+      <c r="J190" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
     </row>
@@ -10951,7 +11428,9 @@
       <c r="G191" s="3"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
-      <c r="J191" s="6"/>
+      <c r="J191" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
     </row>
@@ -10975,7 +11454,9 @@
       <c r="G192" s="3"/>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
-      <c r="J192" s="6"/>
+      <c r="J192" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
     </row>
@@ -11001,7 +11482,9 @@
       <c r="G193" s="3"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
-      <c r="J193" s="6"/>
+      <c r="J193" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
     </row>
@@ -11031,7 +11514,9 @@
         <v>614</v>
       </c>
       <c r="I194" s="4"/>
-      <c r="J194" s="6"/>
+      <c r="J194" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
     </row>
@@ -11055,7 +11540,9 @@
       <c r="G195" s="3"/>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
-      <c r="J195" s="6"/>
+      <c r="J195" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
     </row>
@@ -11081,7 +11568,9 @@
       <c r="G196" s="3"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
-      <c r="J196" s="6"/>
+      <c r="J196" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
     </row>
@@ -11105,7 +11594,9 @@
       <c r="G197" s="3"/>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
-      <c r="J197" s="6"/>
+      <c r="J197" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
     </row>
@@ -11129,7 +11620,9 @@
       <c r="G198" s="3"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
-      <c r="J198" s="6"/>
+      <c r="J198" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
     </row>
@@ -11153,7 +11646,9 @@
       <c r="G199" s="3"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
-      <c r="J199" s="6"/>
+      <c r="J199" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
     </row>
@@ -11177,7 +11672,9 @@
       <c r="G200" s="3"/>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
-      <c r="J200" s="6"/>
+      <c r="J200" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
     </row>
@@ -11201,7 +11698,9 @@
       <c r="G201" s="3"/>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
-      <c r="J201" s="6"/>
+      <c r="J201" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
     </row>
@@ -11225,7 +11724,9 @@
       <c r="G202" s="3"/>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
-      <c r="J202" s="6"/>
+      <c r="J202" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
     </row>
@@ -11249,7 +11750,9 @@
       <c r="G203" s="3"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
-      <c r="J203" s="6"/>
+      <c r="J203" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
     </row>
@@ -11273,7 +11776,9 @@
       <c r="G204" s="3"/>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
-      <c r="J204" s="6"/>
+      <c r="J204" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
     </row>
@@ -11297,7 +11802,9 @@
       <c r="G205" s="3"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
-      <c r="J205" s="6"/>
+      <c r="J205" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
     </row>
@@ -11321,7 +11828,9 @@
       <c r="G206" s="3"/>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
-      <c r="J206" s="6"/>
+      <c r="J206" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
     </row>
@@ -11345,7 +11854,9 @@
       <c r="G207" s="3"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
-      <c r="J207" s="6"/>
+      <c r="J207" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
     </row>
@@ -11369,7 +11880,9 @@
       <c r="G208" s="3"/>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
-      <c r="J208" s="6"/>
+      <c r="J208" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
     </row>
@@ -11393,7 +11906,9 @@
       <c r="G209" s="3"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
-      <c r="J209" s="6"/>
+      <c r="J209" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
     </row>
@@ -11417,7 +11932,9 @@
       <c r="G210" s="3"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
-      <c r="J210" s="6"/>
+      <c r="J210" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
     </row>
@@ -11441,7 +11958,9 @@
       <c r="G211" s="3"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
-      <c r="J211" s="6"/>
+      <c r="J211" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
     </row>
@@ -11465,7 +11984,9 @@
       <c r="G212" s="3"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
-      <c r="J212" s="6"/>
+      <c r="J212" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
     </row>
@@ -11489,7 +12010,9 @@
       <c r="G213" s="3"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
-      <c r="J213" s="6"/>
+      <c r="J213" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
     </row>
@@ -11513,7 +12036,9 @@
       <c r="G214" s="3"/>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
-      <c r="J214" s="6"/>
+      <c r="J214" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
     </row>
@@ -11537,7 +12062,9 @@
       <c r="G215" s="3"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
-      <c r="J215" s="6"/>
+      <c r="J215" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
     </row>
@@ -11561,7 +12088,9 @@
       <c r="G216" s="3"/>
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
-      <c r="J216" s="6"/>
+      <c r="J216" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
     </row>
@@ -11585,7 +12114,9 @@
       <c r="G217" s="3"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
-      <c r="J217" s="6"/>
+      <c r="J217" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
     </row>
@@ -11609,7 +12140,9 @@
       <c r="G218" s="3"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
-      <c r="J218" s="6"/>
+      <c r="J218" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
     </row>
@@ -11633,7 +12166,9 @@
       <c r="G219" s="3"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
-      <c r="J219" s="6"/>
+      <c r="J219" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
     </row>
@@ -11657,7 +12192,9 @@
       <c r="G220" s="3"/>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
-      <c r="J220" s="6"/>
+      <c r="J220" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
     </row>
@@ -11681,7 +12218,9 @@
       <c r="G221" s="3"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
-      <c r="J221" s="6"/>
+      <c r="J221" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
     </row>
@@ -11705,7 +12244,9 @@
       <c r="G222" s="3"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
-      <c r="J222" s="6"/>
+      <c r="J222" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
     </row>
@@ -11729,7 +12270,9 @@
       <c r="G223" s="3"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
-      <c r="J223" s="6"/>
+      <c r="J223" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
     </row>
@@ -11753,7 +12296,9 @@
       <c r="G224" s="3"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
-      <c r="J224" s="6"/>
+      <c r="J224" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
     </row>
@@ -11777,7 +12322,9 @@
       <c r="G225" s="3"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
-      <c r="J225" s="6"/>
+      <c r="J225" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
     </row>
@@ -11801,7 +12348,9 @@
       <c r="G226" s="3"/>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
-      <c r="J226" s="6"/>
+      <c r="J226" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
     </row>
@@ -11825,7 +12374,9 @@
       <c r="G227" s="3"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
-      <c r="J227" s="6"/>
+      <c r="J227" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
     </row>
@@ -11849,7 +12400,9 @@
       <c r="G228" s="3"/>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
-      <c r="J228" s="6"/>
+      <c r="J228" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
     </row>
@@ -11873,7 +12426,9 @@
       <c r="G229" s="3"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
-      <c r="J229" s="6"/>
+      <c r="J229" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
     </row>
@@ -11899,7 +12454,9 @@
       <c r="G230" s="3"/>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
-      <c r="J230" s="6"/>
+      <c r="J230" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
     </row>
@@ -11923,7 +12480,9 @@
       <c r="G231" s="3"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
-      <c r="J231" s="6"/>
+      <c r="J231" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
     </row>
@@ -11953,7 +12512,9 @@
         <v>724</v>
       </c>
       <c r="I232" s="4"/>
-      <c r="J232" s="6"/>
+      <c r="J232" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
     </row>
@@ -11979,8 +12540,12 @@
       <c r="I233" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="J233" s="6"/>
-      <c r="K233" s="7"/>
+      <c r="J233" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K233" s="7" t="s">
+        <v>1810</v>
+      </c>
       <c r="L233" s="7"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.2">
@@ -12003,7 +12568,9 @@
       <c r="G234" s="3"/>
       <c r="H234" s="4"/>
       <c r="I234" s="4"/>
-      <c r="J234" s="6"/>
+      <c r="J234" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
     </row>
@@ -12033,7 +12600,9 @@
         <v>735</v>
       </c>
       <c r="I235" s="4"/>
-      <c r="J235" s="6"/>
+      <c r="J235" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
     </row>
@@ -12063,7 +12632,9 @@
         <v>740</v>
       </c>
       <c r="I236" s="4"/>
-      <c r="J236" s="6"/>
+      <c r="J236" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
     </row>
@@ -12087,7 +12658,9 @@
       <c r="G237" s="3"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
-      <c r="J237" s="6"/>
+      <c r="J237" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
     </row>
@@ -12117,7 +12690,9 @@
         <v>748</v>
       </c>
       <c r="I238" s="4"/>
-      <c r="J238" s="6"/>
+      <c r="J238" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
     </row>
@@ -12141,7 +12716,9 @@
       <c r="G239" s="3"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
-      <c r="J239" s="6"/>
+      <c r="J239" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
     </row>
@@ -12165,7 +12742,9 @@
       <c r="G240" s="3"/>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
-      <c r="J240" s="6"/>
+      <c r="J240" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
     </row>
@@ -12195,7 +12774,9 @@
         <v>759</v>
       </c>
       <c r="I241" s="4"/>
-      <c r="J241" s="6"/>
+      <c r="J241" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
     </row>
@@ -12221,7 +12802,9 @@
       <c r="G242" s="3"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
-      <c r="J242" s="6"/>
+      <c r="J242" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
     </row>
@@ -12245,7 +12828,9 @@
       <c r="G243" s="3"/>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
-      <c r="J243" s="6"/>
+      <c r="J243" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
     </row>
@@ -12273,7 +12858,9 @@
       <c r="I244" s="9" t="s">
         <v>769</v>
       </c>
-      <c r="J244" s="6"/>
+      <c r="J244" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
     </row>
@@ -12297,7 +12884,9 @@
       <c r="G245" s="3"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
-      <c r="J245" s="6"/>
+      <c r="J245" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
     </row>
@@ -12321,7 +12910,9 @@
       <c r="G246" s="3"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
-      <c r="J246" s="6"/>
+      <c r="J246" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
     </row>
@@ -12345,7 +12936,9 @@
       <c r="G247" s="3"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
-      <c r="J247" s="6"/>
+      <c r="J247" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
     </row>
@@ -12369,7 +12962,9 @@
       <c r="G248" s="3"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
-      <c r="J248" s="6"/>
+      <c r="J248" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
     </row>
@@ -12393,7 +12988,9 @@
       <c r="G249" s="3"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
-      <c r="J249" s="6"/>
+      <c r="J249" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
     </row>
@@ -12417,7 +13014,9 @@
       <c r="G250" s="3"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
-      <c r="J250" s="6"/>
+      <c r="J250" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
     </row>
@@ -12441,7 +13040,9 @@
       <c r="G251" s="3"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
-      <c r="J251" s="6"/>
+      <c r="J251" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
     </row>
@@ -12467,7 +13068,9 @@
       <c r="G252" s="3"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
-      <c r="J252" s="6"/>
+      <c r="J252" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
     </row>
@@ -12497,7 +13100,9 @@
         <v>798</v>
       </c>
       <c r="I253" s="4"/>
-      <c r="J253" s="6"/>
+      <c r="J253" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
     </row>
@@ -12521,7 +13126,9 @@
       <c r="G254" s="3"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
-      <c r="J254" s="6"/>
+      <c r="J254" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
     </row>
@@ -12545,7 +13152,9 @@
       <c r="G255" s="3"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
-      <c r="J255" s="6"/>
+      <c r="J255" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
     </row>
@@ -12569,7 +13178,9 @@
       <c r="G256" s="3"/>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
-      <c r="J256" s="6"/>
+      <c r="J256" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
     </row>
@@ -12595,7 +13206,9 @@
       <c r="G257" s="3"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
-      <c r="J257" s="6"/>
+      <c r="J257" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
     </row>
@@ -12619,7 +13232,9 @@
       <c r="G258" s="3"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
-      <c r="J258" s="6"/>
+      <c r="J258" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
     </row>
@@ -12649,7 +13264,9 @@
         <v>818</v>
       </c>
       <c r="I259" s="4"/>
-      <c r="J259" s="6"/>
+      <c r="J259" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
     </row>
@@ -12679,7 +13296,9 @@
         <v>823</v>
       </c>
       <c r="I260" s="4"/>
-      <c r="J260" s="6"/>
+      <c r="J260" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
     </row>
@@ -12709,7 +13328,9 @@
         <v>828</v>
       </c>
       <c r="I261" s="4"/>
-      <c r="J261" s="6"/>
+      <c r="J261" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
     </row>
@@ -12735,7 +13356,9 @@
       <c r="G262" s="3"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
-      <c r="J262" s="6"/>
+      <c r="J262" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
     </row>
@@ -12763,7 +13386,9 @@
         <v>836</v>
       </c>
       <c r="I263" s="4"/>
-      <c r="J263" s="6"/>
+      <c r="J263" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
     </row>
@@ -12787,7 +13412,9 @@
       <c r="G264" s="3"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
-      <c r="J264" s="6"/>
+      <c r="J264" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
     </row>
@@ -12815,7 +13442,9 @@
         <v>844</v>
       </c>
       <c r="I265" s="4"/>
-      <c r="J265" s="6"/>
+      <c r="J265" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
     </row>
@@ -12839,7 +13468,9 @@
       <c r="G266" s="3"/>
       <c r="H266" s="4"/>
       <c r="I266" s="4"/>
-      <c r="J266" s="6"/>
+      <c r="J266" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
     </row>
@@ -12863,7 +13494,9 @@
       <c r="G267" s="3"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
-      <c r="J267" s="6"/>
+      <c r="J267" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
     </row>
@@ -12887,7 +13520,9 @@
       <c r="G268" s="3"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
-      <c r="J268" s="6"/>
+      <c r="J268" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
     </row>
@@ -12911,7 +13546,9 @@
       <c r="G269" s="3"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
-      <c r="J269" s="6"/>
+      <c r="J269" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
     </row>
@@ -12937,7 +13574,9 @@
       <c r="G270" s="3"/>
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
-      <c r="J270" s="6"/>
+      <c r="J270" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
     </row>
@@ -12963,7 +13602,9 @@
       <c r="G271" s="3"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
-      <c r="J271" s="6"/>
+      <c r="J271" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
     </row>
@@ -12989,7 +13630,9 @@
       <c r="G272" s="3"/>
       <c r="H272" s="4"/>
       <c r="I272" s="4"/>
-      <c r="J272" s="6"/>
+      <c r="J272" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
     </row>
@@ -13015,7 +13658,9 @@
         <v>866</v>
       </c>
       <c r="I273" s="4"/>
-      <c r="J273" s="6"/>
+      <c r="J273" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
     </row>
@@ -13041,7 +13686,9 @@
         <v>870</v>
       </c>
       <c r="I274" s="4"/>
-      <c r="J274" s="6"/>
+      <c r="J274" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
     </row>
@@ -13067,7 +13714,9 @@
       <c r="G275" s="3"/>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
-      <c r="J275" s="6"/>
+      <c r="J275" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
     </row>
@@ -13091,7 +13740,9 @@
       <c r="G276" s="3"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
-      <c r="J276" s="6"/>
+      <c r="J276" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
     </row>
@@ -13115,7 +13766,9 @@
       <c r="G277" s="3"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
-      <c r="J277" s="6"/>
+      <c r="J277" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
     </row>
@@ -13139,7 +13792,9 @@
       <c r="G278" s="3"/>
       <c r="H278" s="4"/>
       <c r="I278" s="4"/>
-      <c r="J278" s="6"/>
+      <c r="J278" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
     </row>
@@ -13163,7 +13818,9 @@
       <c r="G279" s="3"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
-      <c r="J279" s="6"/>
+      <c r="J279" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
     </row>
@@ -13189,7 +13846,9 @@
       <c r="G280" s="3"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
-      <c r="J280" s="6"/>
+      <c r="J280" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
     </row>
@@ -13215,7 +13874,9 @@
       <c r="G281" s="3"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
-      <c r="J281" s="6"/>
+      <c r="J281" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
     </row>
@@ -13245,7 +13906,9 @@
         <v>892</v>
       </c>
       <c r="I282" s="4"/>
-      <c r="J282" s="6"/>
+      <c r="J282" s="6" t="s">
+        <v>1808</v>
+      </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
     </row>
@@ -13271,7 +13934,9 @@
       <c r="G283" s="3"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
-      <c r="J283" s="6"/>
+      <c r="J283" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
     </row>
@@ -13297,7 +13962,9 @@
       <c r="G284" s="3"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
-      <c r="J284" s="6"/>
+      <c r="J284" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
     </row>
@@ -13323,7 +13990,9 @@
       <c r="G285" s="3"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
-      <c r="J285" s="6"/>
+      <c r="J285" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
     </row>
@@ -13349,7 +14018,9 @@
       <c r="G286" s="3"/>
       <c r="H286" s="4"/>
       <c r="I286" s="4"/>
-      <c r="J286" s="6"/>
+      <c r="J286" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
     </row>
@@ -13379,7 +14050,9 @@
         <v>907</v>
       </c>
       <c r="I287" s="4"/>
-      <c r="J287" s="6"/>
+      <c r="J287" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
     </row>
@@ -13405,7 +14078,9 @@
       <c r="G288" s="3"/>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
-      <c r="J288" s="6"/>
+      <c r="J288" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
     </row>
@@ -13431,7 +14106,9 @@
       <c r="G289" s="3"/>
       <c r="H289" s="4"/>
       <c r="I289" s="4"/>
-      <c r="J289" s="6"/>
+      <c r="J289" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
     </row>
@@ -13457,7 +14134,9 @@
       <c r="G290" s="3"/>
       <c r="H290" s="4"/>
       <c r="I290" s="4"/>
-      <c r="J290" s="6"/>
+      <c r="J290" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
     </row>
@@ -13481,7 +14160,9 @@
       <c r="G291" s="3"/>
       <c r="H291" s="4"/>
       <c r="I291" s="4"/>
-      <c r="J291" s="6"/>
+      <c r="J291" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
     </row>
@@ -13505,7 +14186,9 @@
       <c r="G292" s="3"/>
       <c r="H292" s="4"/>
       <c r="I292" s="4"/>
-      <c r="J292" s="6"/>
+      <c r="J292" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
     </row>
@@ -13529,7 +14212,9 @@
       <c r="G293" s="3"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
-      <c r="J293" s="6"/>
+      <c r="J293" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
     </row>
@@ -13555,7 +14240,9 @@
       <c r="G294" s="3"/>
       <c r="H294" s="4"/>
       <c r="I294" s="4"/>
-      <c r="J294" s="6"/>
+      <c r="J294" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
     </row>
@@ -13579,7 +14266,9 @@
       <c r="G295" s="3"/>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
-      <c r="J295" s="6"/>
+      <c r="J295" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
     </row>
@@ -13603,7 +14292,9 @@
       <c r="G296" s="3"/>
       <c r="H296" s="4"/>
       <c r="I296" s="4"/>
-      <c r="J296" s="6"/>
+      <c r="J296" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
     </row>
@@ -13629,7 +14320,9 @@
       <c r="G297" s="3"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
-      <c r="J297" s="6"/>
+      <c r="J297" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
     </row>
@@ -13653,7 +14346,9 @@
       <c r="G298" s="3"/>
       <c r="H298" s="4"/>
       <c r="I298" s="4"/>
-      <c r="J298" s="6"/>
+      <c r="J298" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
     </row>
@@ -13677,7 +14372,9 @@
       <c r="G299" s="3"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
-      <c r="J299" s="6"/>
+      <c r="J299" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
     </row>
@@ -13701,7 +14398,9 @@
       <c r="G300" s="3"/>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
-      <c r="J300" s="6"/>
+      <c r="J300" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
     </row>
@@ -13731,7 +14430,9 @@
         <v>950</v>
       </c>
       <c r="I301" s="4"/>
-      <c r="J301" s="6"/>
+      <c r="J301" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
     </row>
@@ -13755,7 +14456,9 @@
       <c r="G302" s="3"/>
       <c r="H302" s="4"/>
       <c r="I302" s="4"/>
-      <c r="J302" s="6"/>
+      <c r="J302" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
     </row>
@@ -13779,7 +14482,9 @@
       <c r="G303" s="3"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
-      <c r="J303" s="6"/>
+      <c r="J303" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
     </row>
@@ -13803,7 +14508,9 @@
       <c r="G304" s="3"/>
       <c r="H304" s="4"/>
       <c r="I304" s="4"/>
-      <c r="J304" s="6"/>
+      <c r="J304" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
     </row>
@@ -13827,7 +14534,9 @@
       <c r="G305" s="3"/>
       <c r="H305" s="4"/>
       <c r="I305" s="4"/>
-      <c r="J305" s="6"/>
+      <c r="J305" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
     </row>
@@ -13851,7 +14560,9 @@
       <c r="G306" s="3"/>
       <c r="H306" s="4"/>
       <c r="I306" s="4"/>
-      <c r="J306" s="6"/>
+      <c r="J306" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
     </row>
@@ -13879,7 +14590,9 @@
         <v>964</v>
       </c>
       <c r="I307" s="4"/>
-      <c r="J307" s="6"/>
+      <c r="J307" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
     </row>
@@ -13903,7 +14616,9 @@
       <c r="G308" s="3"/>
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
-      <c r="J308" s="6"/>
+      <c r="J308" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
     </row>
@@ -13927,7 +14642,9 @@
       <c r="G309" s="3"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
-      <c r="J309" s="6"/>
+      <c r="J309" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
     </row>
@@ -13951,7 +14668,9 @@
       <c r="G310" s="3"/>
       <c r="H310" s="4"/>
       <c r="I310" s="4"/>
-      <c r="J310" s="6"/>
+      <c r="J310" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
     </row>
@@ -13975,7 +14694,9 @@
       <c r="G311" s="3"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
-      <c r="J311" s="6"/>
+      <c r="J311" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
     </row>
@@ -14003,7 +14724,9 @@
         <v>979</v>
       </c>
       <c r="I312" s="4"/>
-      <c r="J312" s="6"/>
+      <c r="J312" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
     </row>
@@ -14027,7 +14750,9 @@
       <c r="G313" s="3"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
-      <c r="J313" s="6"/>
+      <c r="J313" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
     </row>
@@ -14051,7 +14776,9 @@
       <c r="G314" s="3"/>
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
-      <c r="J314" s="6"/>
+      <c r="J314" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
     </row>
@@ -14075,7 +14802,9 @@
       <c r="G315" s="3"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
-      <c r="J315" s="6"/>
+      <c r="J315" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
     </row>
@@ -14099,7 +14828,9 @@
       <c r="G316" s="3"/>
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
-      <c r="J316" s="6"/>
+      <c r="J316" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
     </row>
@@ -14123,7 +14854,9 @@
       <c r="G317" s="3"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
-      <c r="J317" s="6"/>
+      <c r="J317" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
     </row>
@@ -14147,7 +14880,9 @@
       <c r="G318" s="3"/>
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
-      <c r="J318" s="6"/>
+      <c r="J318" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
     </row>
@@ -14171,7 +14906,9 @@
       <c r="G319" s="3"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
-      <c r="J319" s="6"/>
+      <c r="J319" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
     </row>
@@ -14195,7 +14932,9 @@
       <c r="G320" s="3"/>
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
-      <c r="J320" s="6"/>
+      <c r="J320" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
     </row>
@@ -14219,7 +14958,9 @@
       <c r="G321" s="3"/>
       <c r="H321" s="4"/>
       <c r="I321" s="4"/>
-      <c r="J321" s="6"/>
+      <c r="J321" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
     </row>
@@ -14243,7 +14984,9 @@
       <c r="G322" s="3"/>
       <c r="H322" s="4"/>
       <c r="I322" s="4"/>
-      <c r="J322" s="6"/>
+      <c r="J322" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
     </row>
@@ -14267,7 +15010,9 @@
       <c r="G323" s="3"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
-      <c r="J323" s="6"/>
+      <c r="J323" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
     </row>
@@ -14291,7 +15036,9 @@
       <c r="G324" s="3"/>
       <c r="H324" s="4"/>
       <c r="I324" s="4"/>
-      <c r="J324" s="6"/>
+      <c r="J324" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
     </row>
@@ -14315,7 +15062,9 @@
       <c r="G325" s="3"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
-      <c r="J325" s="6"/>
+      <c r="J325" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
     </row>
@@ -14339,7 +15088,9 @@
       <c r="G326" s="3"/>
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
-      <c r="J326" s="6"/>
+      <c r="J326" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
     </row>
@@ -14365,7 +15116,9 @@
       <c r="I327" s="9" t="s">
         <v>1015</v>
       </c>
-      <c r="J327" s="6"/>
+      <c r="J327" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
     </row>
@@ -14389,7 +15142,9 @@
       <c r="G328" s="3"/>
       <c r="H328" s="4"/>
       <c r="I328" s="4"/>
-      <c r="J328" s="6"/>
+      <c r="J328" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
     </row>
@@ -14413,7 +15168,9 @@
       <c r="G329" s="3"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
-      <c r="J329" s="6"/>
+      <c r="J329" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
     </row>
@@ -14437,7 +15194,9 @@
       <c r="G330" s="3"/>
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
-      <c r="J330" s="6"/>
+      <c r="J330" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
     </row>
@@ -14461,7 +15220,9 @@
       <c r="G331" s="3"/>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
-      <c r="J331" s="6"/>
+      <c r="J331" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
     </row>
@@ -14487,7 +15248,9 @@
         <v>1031</v>
       </c>
       <c r="I332" s="4"/>
-      <c r="J332" s="6"/>
+      <c r="J332" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
     </row>
@@ -14513,7 +15276,9 @@
       <c r="I333" s="9" t="s">
         <v>1035</v>
       </c>
-      <c r="J333" s="6"/>
+      <c r="J333" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
     </row>
@@ -14537,7 +15302,9 @@
       <c r="G334" s="3"/>
       <c r="H334" s="4"/>
       <c r="I334" s="4"/>
-      <c r="J334" s="6"/>
+      <c r="J334" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
     </row>
@@ -14561,7 +15328,9 @@
       <c r="G335" s="3"/>
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
-      <c r="J335" s="6"/>
+      <c r="J335" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
     </row>
@@ -14585,7 +15354,9 @@
       <c r="G336" s="3"/>
       <c r="H336" s="4"/>
       <c r="I336" s="4"/>
-      <c r="J336" s="6"/>
+      <c r="J336" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
     </row>
@@ -14609,7 +15380,9 @@
       <c r="G337" s="3"/>
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
-      <c r="J337" s="6"/>
+      <c r="J337" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
     </row>
@@ -14633,7 +15406,9 @@
       <c r="G338" s="3"/>
       <c r="H338" s="4"/>
       <c r="I338" s="4"/>
-      <c r="J338" s="6"/>
+      <c r="J338" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
     </row>
@@ -14657,7 +15432,9 @@
       <c r="G339" s="3"/>
       <c r="H339" s="4"/>
       <c r="I339" s="4"/>
-      <c r="J339" s="6"/>
+      <c r="J339" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
     </row>
@@ -14681,7 +15458,9 @@
       <c r="G340" s="3"/>
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
-      <c r="J340" s="6"/>
+      <c r="J340" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
     </row>
@@ -14705,7 +15484,9 @@
       <c r="G341" s="3"/>
       <c r="H341" s="4"/>
       <c r="I341" s="4"/>
-      <c r="J341" s="6"/>
+      <c r="J341" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
     </row>
@@ -14729,7 +15510,9 @@
       <c r="G342" s="3"/>
       <c r="H342" s="4"/>
       <c r="I342" s="4"/>
-      <c r="J342" s="6"/>
+      <c r="J342" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
     </row>
@@ -14753,7 +15536,9 @@
       <c r="G343" s="3"/>
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
-      <c r="J343" s="6"/>
+      <c r="J343" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
     </row>
@@ -14777,7 +15562,9 @@
       <c r="G344" s="3"/>
       <c r="H344" s="4"/>
       <c r="I344" s="4"/>
-      <c r="J344" s="6"/>
+      <c r="J344" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
     </row>
@@ -14801,7 +15588,9 @@
       <c r="G345" s="3"/>
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
-      <c r="J345" s="6"/>
+      <c r="J345" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
     </row>
@@ -14827,7 +15616,9 @@
       <c r="I346" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="J346" s="6"/>
+      <c r="J346" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
     </row>
@@ -14851,7 +15642,9 @@
       <c r="G347" s="3"/>
       <c r="H347" s="4"/>
       <c r="I347" s="4"/>
-      <c r="J347" s="6"/>
+      <c r="J347" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
     </row>
@@ -14879,7 +15672,9 @@
         <v>1072</v>
       </c>
       <c r="I348" s="4"/>
-      <c r="J348" s="6"/>
+      <c r="J348" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
     </row>
@@ -14903,7 +15698,9 @@
       <c r="G349" s="3"/>
       <c r="H349" s="4"/>
       <c r="I349" s="4"/>
-      <c r="J349" s="6"/>
+      <c r="J349" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
     </row>
@@ -14927,7 +15724,9 @@
       <c r="G350" s="3"/>
       <c r="H350" s="4"/>
       <c r="I350" s="4"/>
-      <c r="J350" s="6"/>
+      <c r="J350" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
     </row>
@@ -14951,7 +15750,9 @@
       <c r="G351" s="3"/>
       <c r="H351" s="4"/>
       <c r="I351" s="4"/>
-      <c r="J351" s="6"/>
+      <c r="J351" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
     </row>
@@ -14975,7 +15776,9 @@
       <c r="G352" s="3"/>
       <c r="H352" s="4"/>
       <c r="I352" s="4"/>
-      <c r="J352" s="6"/>
+      <c r="J352" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
     </row>
@@ -14999,7 +15802,9 @@
       <c r="G353" s="3"/>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
-      <c r="J353" s="6"/>
+      <c r="J353" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
     </row>
@@ -15023,7 +15828,9 @@
       <c r="G354" s="3"/>
       <c r="H354" s="4"/>
       <c r="I354" s="4"/>
-      <c r="J354" s="6"/>
+      <c r="J354" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
     </row>
@@ -15047,7 +15854,9 @@
       <c r="G355" s="3"/>
       <c r="H355" s="4"/>
       <c r="I355" s="4"/>
-      <c r="J355" s="6"/>
+      <c r="J355" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
     </row>
@@ -15071,7 +15880,9 @@
       <c r="G356" s="3"/>
       <c r="H356" s="4"/>
       <c r="I356" s="4"/>
-      <c r="J356" s="6"/>
+      <c r="J356" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
     </row>
@@ -15095,7 +15906,9 @@
       <c r="G357" s="3"/>
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
-      <c r="J357" s="6"/>
+      <c r="J357" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
     </row>
@@ -15119,7 +15932,9 @@
       <c r="G358" s="3"/>
       <c r="H358" s="4"/>
       <c r="I358" s="4"/>
-      <c r="J358" s="6"/>
+      <c r="J358" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
     </row>
@@ -15143,7 +15958,9 @@
       <c r="G359" s="3"/>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
-      <c r="J359" s="6"/>
+      <c r="J359" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
     </row>
@@ -15171,7 +15988,9 @@
         <v>1109</v>
       </c>
       <c r="I360" s="4"/>
-      <c r="J360" s="6"/>
+      <c r="J360" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
     </row>
@@ -15195,7 +16014,9 @@
       <c r="G361" s="3"/>
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
-      <c r="J361" s="6"/>
+      <c r="J361" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
     </row>
@@ -15219,7 +16040,9 @@
       <c r="G362" s="3"/>
       <c r="H362" s="4"/>
       <c r="I362" s="4"/>
-      <c r="J362" s="6"/>
+      <c r="J362" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
     </row>
@@ -15243,7 +16066,9 @@
       <c r="G363" s="3"/>
       <c r="H363" s="4"/>
       <c r="I363" s="4"/>
-      <c r="J363" s="6"/>
+      <c r="J363" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
     </row>
@@ -15267,7 +16092,9 @@
       <c r="G364" s="3"/>
       <c r="H364" s="4"/>
       <c r="I364" s="4"/>
-      <c r="J364" s="6"/>
+      <c r="J364" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
     </row>
@@ -15291,7 +16118,9 @@
       <c r="G365" s="3"/>
       <c r="H365" s="4"/>
       <c r="I365" s="4"/>
-      <c r="J365" s="6"/>
+      <c r="J365" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
     </row>
@@ -15315,7 +16144,9 @@
       <c r="G366" s="3"/>
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
-      <c r="J366" s="6"/>
+      <c r="J366" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
     </row>
@@ -15339,7 +16170,9 @@
       <c r="G367" s="3"/>
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
-      <c r="J367" s="6"/>
+      <c r="J367" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
     </row>
@@ -15363,7 +16196,9 @@
       <c r="G368" s="3"/>
       <c r="H368" s="4"/>
       <c r="I368" s="4"/>
-      <c r="J368" s="6"/>
+      <c r="J368" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
     </row>
@@ -15387,7 +16222,9 @@
       <c r="G369" s="3"/>
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
-      <c r="J369" s="6"/>
+      <c r="J369" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
     </row>
@@ -15413,7 +16250,9 @@
         <v>1138</v>
       </c>
       <c r="I370" s="4"/>
-      <c r="J370" s="6"/>
+      <c r="J370" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
     </row>
@@ -15437,7 +16276,9 @@
       <c r="G371" s="3"/>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
-      <c r="J371" s="6"/>
+      <c r="J371" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
     </row>
@@ -15461,7 +16302,9 @@
       <c r="G372" s="3"/>
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
-      <c r="J372" s="6"/>
+      <c r="J372" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
     </row>
@@ -15485,7 +16328,9 @@
       <c r="G373" s="3"/>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
-      <c r="J373" s="6"/>
+      <c r="J373" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
     </row>
@@ -15511,7 +16356,9 @@
       <c r="I374" s="9" t="s">
         <v>1151</v>
       </c>
-      <c r="J374" s="6"/>
+      <c r="J374" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
     </row>
@@ -15535,7 +16382,9 @@
       <c r="G375" s="3"/>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
-      <c r="J375" s="6"/>
+      <c r="J375" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
     </row>
@@ -15559,7 +16408,9 @@
       <c r="G376" s="3"/>
       <c r="H376" s="4"/>
       <c r="I376" s="4"/>
-      <c r="J376" s="6"/>
+      <c r="J376" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
     </row>
@@ -15583,7 +16434,9 @@
       <c r="G377" s="3"/>
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
-      <c r="J377" s="6"/>
+      <c r="J377" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
     </row>
@@ -15611,7 +16464,9 @@
         <v>1164</v>
       </c>
       <c r="I378" s="4"/>
-      <c r="J378" s="6"/>
+      <c r="J378" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
     </row>
@@ -15635,7 +16490,9 @@
       <c r="G379" s="3"/>
       <c r="H379" s="4"/>
       <c r="I379" s="4"/>
-      <c r="J379" s="6"/>
+      <c r="J379" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
     </row>
@@ -15659,7 +16516,9 @@
       <c r="G380" s="3"/>
       <c r="H380" s="4"/>
       <c r="I380" s="4"/>
-      <c r="J380" s="6"/>
+      <c r="J380" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
     </row>
@@ -15683,7 +16542,9 @@
       <c r="G381" s="3"/>
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
-      <c r="J381" s="6"/>
+      <c r="J381" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
     </row>
@@ -15707,7 +16568,9 @@
       <c r="G382" s="3"/>
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
-      <c r="J382" s="6"/>
+      <c r="J382" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
     </row>
@@ -15731,7 +16594,9 @@
       <c r="G383" s="3"/>
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
-      <c r="J383" s="6"/>
+      <c r="J383" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
     </row>
@@ -15755,7 +16620,9 @@
       <c r="G384" s="3"/>
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
-      <c r="J384" s="6"/>
+      <c r="J384" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
     </row>
@@ -15779,7 +16646,9 @@
       <c r="G385" s="3"/>
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
-      <c r="J385" s="6"/>
+      <c r="J385" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
     </row>
@@ -15805,7 +16674,9 @@
         <v>1189</v>
       </c>
       <c r="I386" s="4"/>
-      <c r="J386" s="6"/>
+      <c r="J386" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
     </row>
@@ -15829,7 +16700,9 @@
       <c r="G387" s="3"/>
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
-      <c r="J387" s="6"/>
+      <c r="J387" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
     </row>
@@ -15853,7 +16726,9 @@
       <c r="G388" s="3"/>
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
-      <c r="J388" s="6"/>
+      <c r="J388" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
     </row>
@@ -15877,7 +16752,9 @@
       <c r="G389" s="3"/>
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
-      <c r="J389" s="6"/>
+      <c r="J389" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
     </row>
@@ -15901,7 +16778,9 @@
       <c r="G390" s="3"/>
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
-      <c r="J390" s="6"/>
+      <c r="J390" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
     </row>
@@ -15927,7 +16806,9 @@
       <c r="I391" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="J391" s="6"/>
+      <c r="J391" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
     </row>
@@ -15951,7 +16832,9 @@
       <c r="G392" s="3"/>
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
-      <c r="J392" s="6"/>
+      <c r="J392" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
     </row>
@@ -15975,7 +16858,9 @@
       <c r="G393" s="3"/>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
-      <c r="J393" s="6"/>
+      <c r="J393" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
     </row>
@@ -15999,7 +16884,9 @@
       <c r="G394" s="3"/>
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
-      <c r="J394" s="6"/>
+      <c r="J394" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
     </row>
@@ -16023,7 +16910,9 @@
       <c r="G395" s="3"/>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
-      <c r="J395" s="6"/>
+      <c r="J395" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
     </row>
@@ -16047,7 +16936,9 @@
       <c r="G396" s="3"/>
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
-      <c r="J396" s="6"/>
+      <c r="J396" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
     </row>
@@ -16071,7 +16962,9 @@
       <c r="G397" s="3"/>
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
-      <c r="J397" s="6"/>
+      <c r="J397" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
     </row>
@@ -16095,7 +16988,9 @@
       <c r="G398" s="3"/>
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
-      <c r="J398" s="6"/>
+      <c r="J398" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
     </row>
@@ -16119,7 +17014,9 @@
       <c r="G399" s="3"/>
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
-      <c r="J399" s="6"/>
+      <c r="J399" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
     </row>
@@ -16145,7 +17042,9 @@
         <v>1232</v>
       </c>
       <c r="I400" s="4"/>
-      <c r="J400" s="6"/>
+      <c r="J400" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
     </row>
@@ -16169,7 +17068,9 @@
       <c r="G401" s="3"/>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
-      <c r="J401" s="6"/>
+      <c r="J401" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
     </row>
@@ -16193,7 +17094,9 @@
       <c r="G402" s="3"/>
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
-      <c r="J402" s="6"/>
+      <c r="J402" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
     </row>
@@ -16217,7 +17120,9 @@
       <c r="G403" s="3"/>
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
-      <c r="J403" s="6"/>
+      <c r="J403" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
     </row>
@@ -16241,7 +17146,9 @@
       <c r="G404" s="3"/>
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
-      <c r="J404" s="6"/>
+      <c r="J404" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
     </row>
@@ -16265,7 +17172,9 @@
       <c r="G405" s="3"/>
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
-      <c r="J405" s="6"/>
+      <c r="J405" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
     </row>
@@ -16291,8 +17200,12 @@
         <v>1251</v>
       </c>
       <c r="I406" s="4"/>
-      <c r="J406" s="6"/>
-      <c r="K406" s="7"/>
+      <c r="J406" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K406" s="7" t="s">
+        <v>1811</v>
+      </c>
       <c r="L406" s="7"/>
     </row>
     <row r="407" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -16317,8 +17230,12 @@
         <v>1255</v>
       </c>
       <c r="I407" s="4"/>
-      <c r="J407" s="6"/>
-      <c r="K407" s="7"/>
+      <c r="J407" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K407" s="7" t="s">
+        <v>1812</v>
+      </c>
       <c r="L407" s="7"/>
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.2">
@@ -16341,7 +17258,9 @@
       <c r="G408" s="3"/>
       <c r="H408" s="4"/>
       <c r="I408" s="4"/>
-      <c r="J408" s="6"/>
+      <c r="J408" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
     </row>
@@ -16365,7 +17284,9 @@
       <c r="G409" s="3"/>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
-      <c r="J409" s="6"/>
+      <c r="J409" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
     </row>
@@ -16393,7 +17314,9 @@
       <c r="I410" s="9" t="s">
         <v>1266</v>
       </c>
-      <c r="J410" s="6"/>
+      <c r="J410" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
     </row>
@@ -16417,7 +17340,9 @@
       <c r="G411" s="3"/>
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
-      <c r="J411" s="6"/>
+      <c r="J411" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
     </row>
@@ -16441,7 +17366,9 @@
       <c r="G412" s="3"/>
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
-      <c r="J412" s="6"/>
+      <c r="J412" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
     </row>
@@ -16465,7 +17392,9 @@
       <c r="G413" s="3"/>
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
-      <c r="J413" s="6"/>
+      <c r="J413" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
     </row>
@@ -16489,7 +17418,9 @@
       <c r="G414" s="3"/>
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
-      <c r="J414" s="6"/>
+      <c r="J414" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
     </row>
@@ -16513,7 +17444,9 @@
       <c r="G415" s="3"/>
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
-      <c r="J415" s="6"/>
+      <c r="J415" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
     </row>
@@ -16539,7 +17472,9 @@
       <c r="I416" s="9" t="s">
         <v>1285</v>
       </c>
-      <c r="J416" s="6"/>
+      <c r="J416" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
     </row>
@@ -16567,7 +17502,9 @@
         <v>1289</v>
       </c>
       <c r="I417" s="4"/>
-      <c r="J417" s="6"/>
+      <c r="J417" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
     </row>
@@ -16591,7 +17528,9 @@
       <c r="G418" s="3"/>
       <c r="H418" s="4"/>
       <c r="I418" s="4"/>
-      <c r="J418" s="6"/>
+      <c r="J418" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
     </row>
@@ -16615,7 +17554,9 @@
       <c r="G419" s="3"/>
       <c r="H419" s="4"/>
       <c r="I419" s="4"/>
-      <c r="J419" s="6"/>
+      <c r="J419" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
     </row>
@@ -16641,7 +17582,9 @@
       <c r="I420" s="9" t="s">
         <v>1151</v>
       </c>
-      <c r="J420" s="6"/>
+      <c r="J420" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
     </row>
@@ -16667,7 +17610,9 @@
         <v>1302</v>
       </c>
       <c r="I421" s="4"/>
-      <c r="J421" s="6"/>
+      <c r="J421" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
     </row>
@@ -16691,7 +17636,9 @@
       <c r="G422" s="3"/>
       <c r="H422" s="4"/>
       <c r="I422" s="4"/>
-      <c r="J422" s="6"/>
+      <c r="J422" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
     </row>
@@ -16715,7 +17662,9 @@
       <c r="G423" s="3"/>
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
-      <c r="J423" s="6"/>
+      <c r="J423" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
     </row>
@@ -16739,7 +17688,9 @@
       <c r="G424" s="3"/>
       <c r="H424" s="4"/>
       <c r="I424" s="4"/>
-      <c r="J424" s="6"/>
+      <c r="J424" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
     </row>
@@ -16763,7 +17714,9 @@
       <c r="G425" s="3"/>
       <c r="H425" s="4"/>
       <c r="I425" s="4"/>
-      <c r="J425" s="6"/>
+      <c r="J425" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
     </row>
@@ -16787,7 +17740,9 @@
       <c r="G426" s="3"/>
       <c r="H426" s="4"/>
       <c r="I426" s="4"/>
-      <c r="J426" s="6"/>
+      <c r="J426" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
     </row>
@@ -16811,7 +17766,9 @@
       <c r="G427" s="3"/>
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
-      <c r="J427" s="6"/>
+      <c r="J427" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
     </row>
@@ -16835,7 +17792,9 @@
       <c r="G428" s="3"/>
       <c r="H428" s="4"/>
       <c r="I428" s="4"/>
-      <c r="J428" s="6"/>
+      <c r="J428" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
     </row>
@@ -16859,7 +17818,9 @@
       <c r="G429" s="3"/>
       <c r="H429" s="4"/>
       <c r="I429" s="4"/>
-      <c r="J429" s="6"/>
+      <c r="J429" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
     </row>
@@ -16883,7 +17844,9 @@
       <c r="G430" s="3"/>
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
-      <c r="J430" s="6"/>
+      <c r="J430" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
     </row>
@@ -16907,7 +17870,9 @@
       <c r="G431" s="3"/>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
-      <c r="J431" s="6"/>
+      <c r="J431" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
     </row>
@@ -16933,7 +17898,9 @@
       <c r="I432" s="9" t="s">
         <v>1336</v>
       </c>
-      <c r="J432" s="6"/>
+      <c r="J432" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
     </row>
@@ -16957,7 +17924,9 @@
       <c r="G433" s="3"/>
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
-      <c r="J433" s="6"/>
+      <c r="J433" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
     </row>
@@ -16983,7 +17952,9 @@
       <c r="I434" s="9" t="s">
         <v>1343</v>
       </c>
-      <c r="J434" s="6"/>
+      <c r="J434" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
     </row>
@@ -17007,7 +17978,9 @@
       <c r="G435" s="3"/>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
-      <c r="J435" s="6"/>
+      <c r="J435" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
     </row>
@@ -17031,7 +18004,9 @@
       <c r="G436" s="3"/>
       <c r="H436" s="4"/>
       <c r="I436" s="4"/>
-      <c r="J436" s="6"/>
+      <c r="J436" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
     </row>
@@ -17055,7 +18030,9 @@
       <c r="G437" s="3"/>
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
-      <c r="J437" s="6"/>
+      <c r="J437" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
     </row>
@@ -17079,7 +18056,9 @@
       <c r="G438" s="3"/>
       <c r="H438" s="4"/>
       <c r="I438" s="4"/>
-      <c r="J438" s="6"/>
+      <c r="J438" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
     </row>
@@ -17103,7 +18082,9 @@
       <c r="G439" s="3"/>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
-      <c r="J439" s="6"/>
+      <c r="J439" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
     </row>
@@ -17129,7 +18110,9 @@
         <v>1362</v>
       </c>
       <c r="I440" s="4"/>
-      <c r="J440" s="6"/>
+      <c r="J440" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
     </row>
@@ -17155,8 +18138,12 @@
       <c r="I441" s="9" t="s">
         <v>1366</v>
       </c>
-      <c r="J441" s="6"/>
-      <c r="K441" s="7"/>
+      <c r="J441" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K441" s="7" t="s">
+        <v>1813</v>
+      </c>
       <c r="L441" s="7"/>
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.2">
@@ -17179,7 +18166,9 @@
       <c r="G442" s="3"/>
       <c r="H442" s="4"/>
       <c r="I442" s="4"/>
-      <c r="J442" s="6"/>
+      <c r="J442" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
     </row>
@@ -17203,7 +18192,9 @@
       <c r="G443" s="3"/>
       <c r="H443" s="4"/>
       <c r="I443" s="4"/>
-      <c r="J443" s="6"/>
+      <c r="J443" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
     </row>
@@ -17227,7 +18218,9 @@
       <c r="G444" s="3"/>
       <c r="H444" s="4"/>
       <c r="I444" s="4"/>
-      <c r="J444" s="6"/>
+      <c r="J444" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
     </row>
@@ -17253,7 +18246,9 @@
         <v>1379</v>
       </c>
       <c r="I445" s="4"/>
-      <c r="J445" s="6"/>
+      <c r="J445" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
     </row>
@@ -17277,7 +18272,9 @@
       <c r="G446" s="3"/>
       <c r="H446" s="4"/>
       <c r="I446" s="4"/>
-      <c r="J446" s="6"/>
+      <c r="J446" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
     </row>
@@ -17301,7 +18298,9 @@
       <c r="G447" s="3"/>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
-      <c r="J447" s="6"/>
+      <c r="J447" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
     </row>
@@ -17325,7 +18324,9 @@
       <c r="G448" s="3"/>
       <c r="H448" s="4"/>
       <c r="I448" s="4"/>
-      <c r="J448" s="6"/>
+      <c r="J448" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
     </row>
@@ -17349,7 +18350,9 @@
       <c r="G449" s="3"/>
       <c r="H449" s="4"/>
       <c r="I449" s="4"/>
-      <c r="J449" s="6"/>
+      <c r="J449" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
     </row>
@@ -17373,7 +18376,9 @@
       <c r="G450" s="3"/>
       <c r="H450" s="4"/>
       <c r="I450" s="4"/>
-      <c r="J450" s="6"/>
+      <c r="J450" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
     </row>
@@ -17397,7 +18402,9 @@
       <c r="G451" s="3"/>
       <c r="H451" s="4"/>
       <c r="I451" s="4"/>
-      <c r="J451" s="6"/>
+      <c r="J451" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
     </row>
@@ -17423,7 +18430,9 @@
       <c r="I452" s="9" t="s">
         <v>1401</v>
       </c>
-      <c r="J452" s="6"/>
+      <c r="J452" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
     </row>
@@ -17447,7 +18456,9 @@
       <c r="G453" s="3"/>
       <c r="H453" s="4"/>
       <c r="I453" s="4"/>
-      <c r="J453" s="6"/>
+      <c r="J453" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
     </row>
@@ -17473,7 +18484,9 @@
       <c r="I454" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="J454" s="6"/>
+      <c r="J454" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
     </row>
@@ -17497,7 +18510,9 @@
       <c r="G455" s="3"/>
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
-      <c r="J455" s="6"/>
+      <c r="J455" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
     </row>
@@ -17521,7 +18536,9 @@
       <c r="G456" s="3"/>
       <c r="H456" s="4"/>
       <c r="I456" s="4"/>
-      <c r="J456" s="6"/>
+      <c r="J456" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
     </row>
@@ -17545,7 +18562,9 @@
       <c r="G457" s="3"/>
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
-      <c r="J457" s="6"/>
+      <c r="J457" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
     </row>
@@ -17571,7 +18590,9 @@
         <v>1420</v>
       </c>
       <c r="I458" s="4"/>
-      <c r="J458" s="6"/>
+      <c r="J458" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
     </row>
@@ -17595,7 +18616,9 @@
       <c r="G459" s="3"/>
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
-      <c r="J459" s="6"/>
+      <c r="J459" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
     </row>
@@ -17619,7 +18642,9 @@
       <c r="G460" s="3"/>
       <c r="H460" s="4"/>
       <c r="I460" s="4"/>
-      <c r="J460" s="6"/>
+      <c r="J460" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
     </row>
@@ -17643,7 +18668,9 @@
       <c r="G461" s="3"/>
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
-      <c r="J461" s="6"/>
+      <c r="J461" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
     </row>
@@ -17667,7 +18694,9 @@
       <c r="G462" s="3"/>
       <c r="H462" s="4"/>
       <c r="I462" s="4"/>
-      <c r="J462" s="6"/>
+      <c r="J462" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
     </row>
@@ -17691,7 +18720,9 @@
       <c r="G463" s="3"/>
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
-      <c r="J463" s="6"/>
+      <c r="J463" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
     </row>
@@ -17721,7 +18752,9 @@
       <c r="I464" s="9" t="s">
         <v>1440</v>
       </c>
-      <c r="J464" s="6"/>
+      <c r="J464" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
     </row>
@@ -17745,7 +18778,9 @@
       <c r="G465" s="3"/>
       <c r="H465" s="4"/>
       <c r="I465" s="4"/>
-      <c r="J465" s="6"/>
+      <c r="J465" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
     </row>
@@ -17775,7 +18810,9 @@
       <c r="I466" s="9" t="s">
         <v>1448</v>
       </c>
-      <c r="J466" s="6"/>
+      <c r="J466" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
     </row>
@@ -17801,7 +18838,9 @@
       <c r="I467" s="9" t="s">
         <v>1452</v>
       </c>
-      <c r="J467" s="6"/>
+      <c r="J467" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
     </row>
@@ -17827,7 +18866,9 @@
       <c r="I468" s="9" t="s">
         <v>1456</v>
       </c>
-      <c r="J468" s="6"/>
+      <c r="J468" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
     </row>
@@ -17853,7 +18894,9 @@
       <c r="I469" s="9" t="s">
         <v>1460</v>
       </c>
-      <c r="J469" s="6"/>
+      <c r="J469" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
     </row>
@@ -17879,7 +18922,9 @@
       <c r="I470" s="9" t="s">
         <v>1464</v>
       </c>
-      <c r="J470" s="6"/>
+      <c r="J470" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
     </row>
@@ -17905,7 +18950,9 @@
       <c r="I471" s="9" t="s">
         <v>1468</v>
       </c>
-      <c r="J471" s="6"/>
+      <c r="J471" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
     </row>
@@ -17931,7 +18978,9 @@
       <c r="I472" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="J472" s="6"/>
+      <c r="J472" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
     </row>
@@ -17957,7 +19006,9 @@
       <c r="I473" s="9" t="s">
         <v>1476</v>
       </c>
-      <c r="J473" s="6"/>
+      <c r="J473" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
     </row>
@@ -17983,7 +19034,9 @@
       <c r="I474" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="J474" s="6"/>
+      <c r="J474" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
     </row>
@@ -18009,7 +19062,9 @@
       <c r="I475" s="9" t="s">
         <v>1483</v>
       </c>
-      <c r="J475" s="6"/>
+      <c r="J475" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
     </row>
@@ -18035,7 +19090,9 @@
       <c r="I476" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="J476" s="6"/>
+      <c r="J476" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
     </row>
@@ -18061,7 +19118,9 @@
       <c r="I477" s="9" t="s">
         <v>1483</v>
       </c>
-      <c r="J477" s="6"/>
+      <c r="J477" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
     </row>
@@ -18087,7 +19146,9 @@
       <c r="I478" s="9" t="s">
         <v>1493</v>
       </c>
-      <c r="J478" s="6"/>
+      <c r="J478" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
     </row>
@@ -18113,7 +19174,9 @@
       <c r="I479" s="9" t="s">
         <v>1497</v>
       </c>
-      <c r="J479" s="6"/>
+      <c r="J479" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
     </row>
@@ -18139,7 +19202,9 @@
       <c r="I480" s="9" t="s">
         <v>1493</v>
       </c>
-      <c r="J480" s="6"/>
+      <c r="J480" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
     </row>
@@ -18165,7 +19230,9 @@
       <c r="I481" s="9" t="s">
         <v>1497</v>
       </c>
-      <c r="J481" s="6"/>
+      <c r="J481" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
     </row>
@@ -18191,7 +19258,9 @@
       <c r="I482" s="9" t="s">
         <v>1493</v>
       </c>
-      <c r="J482" s="6"/>
+      <c r="J482" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
     </row>
@@ -18217,7 +19286,9 @@
       <c r="I483" s="9" t="s">
         <v>1497</v>
       </c>
-      <c r="J483" s="6"/>
+      <c r="J483" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
     </row>
@@ -18241,7 +19312,9 @@
       <c r="G484" s="3"/>
       <c r="H484" s="4"/>
       <c r="I484" s="4"/>
-      <c r="J484" s="6"/>
+      <c r="J484" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
     </row>
@@ -18265,7 +19338,9 @@
       <c r="G485" s="3"/>
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
-      <c r="J485" s="6"/>
+      <c r="J485" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
     </row>
@@ -18289,7 +19364,9 @@
       <c r="G486" s="3"/>
       <c r="H486" s="4"/>
       <c r="I486" s="4"/>
-      <c r="J486" s="6"/>
+      <c r="J486" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
     </row>
@@ -18313,7 +19390,9 @@
       <c r="G487" s="3"/>
       <c r="H487" s="4"/>
       <c r="I487" s="4"/>
-      <c r="J487" s="6"/>
+      <c r="J487" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
     </row>
@@ -18337,7 +19416,9 @@
       <c r="G488" s="3"/>
       <c r="H488" s="4"/>
       <c r="I488" s="4"/>
-      <c r="J488" s="6"/>
+      <c r="J488" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
     </row>
@@ -18361,7 +19442,9 @@
       <c r="G489" s="3"/>
       <c r="H489" s="4"/>
       <c r="I489" s="4"/>
-      <c r="J489" s="6"/>
+      <c r="J489" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
     </row>
@@ -18385,7 +19468,9 @@
       <c r="G490" s="3"/>
       <c r="H490" s="4"/>
       <c r="I490" s="4"/>
-      <c r="J490" s="6"/>
+      <c r="J490" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
     </row>
@@ -18409,7 +19494,9 @@
       <c r="G491" s="3"/>
       <c r="H491" s="4"/>
       <c r="I491" s="4"/>
-      <c r="J491" s="6"/>
+      <c r="J491" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
     </row>
@@ -18433,7 +19520,9 @@
       <c r="G492" s="3"/>
       <c r="H492" s="4"/>
       <c r="I492" s="4"/>
-      <c r="J492" s="6"/>
+      <c r="J492" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
     </row>
@@ -18463,7 +19552,9 @@
         <v>1535</v>
       </c>
       <c r="I493" s="4"/>
-      <c r="J493" s="6"/>
+      <c r="J493" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
     </row>
@@ -18489,7 +19580,9 @@
       <c r="G494" s="3"/>
       <c r="H494" s="4"/>
       <c r="I494" s="4"/>
-      <c r="J494" s="6"/>
+      <c r="J494" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
     </row>
@@ -18513,7 +19606,9 @@
       <c r="G495" s="3"/>
       <c r="H495" s="4"/>
       <c r="I495" s="4"/>
-      <c r="J495" s="6"/>
+      <c r="J495" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
     </row>
@@ -18537,7 +19632,9 @@
       <c r="G496" s="3"/>
       <c r="H496" s="4"/>
       <c r="I496" s="4"/>
-      <c r="J496" s="6"/>
+      <c r="J496" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
     </row>
@@ -18561,7 +19658,9 @@
       <c r="G497" s="3"/>
       <c r="H497" s="4"/>
       <c r="I497" s="4"/>
-      <c r="J497" s="6"/>
+      <c r="J497" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
     </row>
@@ -18585,7 +19684,9 @@
       <c r="G498" s="3"/>
       <c r="H498" s="4"/>
       <c r="I498" s="4"/>
-      <c r="J498" s="6"/>
+      <c r="J498" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
     </row>
@@ -18611,7 +19712,9 @@
         <v>1554</v>
       </c>
       <c r="I499" s="4"/>
-      <c r="J499" s="6"/>
+      <c r="J499" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
     </row>
@@ -18635,8 +19738,12 @@
       <c r="G500" s="3"/>
       <c r="H500" s="4"/>
       <c r="I500" s="4"/>
-      <c r="J500" s="6"/>
-      <c r="K500" s="7"/>
+      <c r="J500" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K500" s="7" t="s">
+        <v>1798</v>
+      </c>
       <c r="L500" s="7"/>
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.2">
@@ -18659,7 +19766,9 @@
       <c r="G501" s="3"/>
       <c r="H501" s="4"/>
       <c r="I501" s="4"/>
-      <c r="J501" s="6"/>
+      <c r="J501" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
     </row>
@@ -18685,7 +19794,9 @@
       <c r="G502" s="3"/>
       <c r="H502" s="4"/>
       <c r="I502" s="4"/>
-      <c r="J502" s="6"/>
+      <c r="J502" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
     </row>
@@ -18709,11 +19820,13 @@
       <c r="G503" s="3"/>
       <c r="H503" s="4"/>
       <c r="I503" s="4"/>
-      <c r="J503" s="6"/>
+      <c r="J503" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
     </row>
-    <row r="504" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A504" s="3" t="s">
         <v>1532</v>
       </c>
@@ -18733,8 +19846,12 @@
       <c r="G504" s="3"/>
       <c r="H504" s="4"/>
       <c r="I504" s="4"/>
-      <c r="J504" s="6"/>
-      <c r="K504" s="7"/>
+      <c r="J504" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K504" s="7" t="s">
+        <v>1814</v>
+      </c>
       <c r="L504" s="7"/>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.2">
@@ -18757,7 +19874,9 @@
       <c r="G505" s="3"/>
       <c r="H505" s="4"/>
       <c r="I505" s="4"/>
-      <c r="J505" s="6"/>
+      <c r="J505" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K505" s="7"/>
       <c r="L505" s="7"/>
     </row>
@@ -18781,7 +19900,9 @@
       <c r="G506" s="3"/>
       <c r="H506" s="4"/>
       <c r="I506" s="4"/>
-      <c r="J506" s="6"/>
+      <c r="J506" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K506" s="7"/>
       <c r="L506" s="7"/>
     </row>
@@ -18807,7 +19928,9 @@
       <c r="I507" s="9" t="s">
         <v>1577</v>
       </c>
-      <c r="J507" s="6"/>
+      <c r="J507" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K507" s="7"/>
       <c r="L507" s="7"/>
     </row>
@@ -18833,7 +19956,9 @@
       <c r="I508" s="9" t="s">
         <v>1581</v>
       </c>
-      <c r="J508" s="6"/>
+      <c r="J508" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K508" s="7"/>
       <c r="L508" s="7"/>
     </row>
@@ -18857,7 +19982,9 @@
       <c r="G509" s="3"/>
       <c r="H509" s="4"/>
       <c r="I509" s="4"/>
-      <c r="J509" s="6"/>
+      <c r="J509" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
     </row>
@@ -18883,7 +20010,9 @@
         <v>1588</v>
       </c>
       <c r="I510" s="4"/>
-      <c r="J510" s="6"/>
+      <c r="J510" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
     </row>
@@ -18907,7 +20036,9 @@
       <c r="G511" s="3"/>
       <c r="H511" s="4"/>
       <c r="I511" s="4"/>
-      <c r="J511" s="6"/>
+      <c r="J511" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K511" s="7"/>
       <c r="L511" s="7"/>
     </row>
@@ -18931,7 +20062,9 @@
       <c r="G512" s="3"/>
       <c r="H512" s="4"/>
       <c r="I512" s="4"/>
-      <c r="J512" s="6"/>
+      <c r="J512" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
     </row>
@@ -18957,7 +20090,9 @@
       <c r="G513" s="3"/>
       <c r="H513" s="4"/>
       <c r="I513" s="4"/>
-      <c r="J513" s="6"/>
+      <c r="J513" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
     </row>
@@ -18983,7 +20118,9 @@
       <c r="I514" s="9" t="s">
         <v>1601</v>
       </c>
-      <c r="J514" s="6"/>
+      <c r="J514" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K514" s="7"/>
       <c r="L514" s="7"/>
     </row>
@@ -19007,7 +20144,9 @@
       <c r="G515" s="3"/>
       <c r="H515" s="4"/>
       <c r="I515" s="4"/>
-      <c r="J515" s="6"/>
+      <c r="J515" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K515" s="7"/>
       <c r="L515" s="7"/>
     </row>
@@ -19031,7 +20170,9 @@
       <c r="G516" s="3"/>
       <c r="H516" s="4"/>
       <c r="I516" s="4"/>
-      <c r="J516" s="6"/>
+      <c r="J516" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
     </row>
@@ -19055,7 +20196,9 @@
       <c r="G517" s="3"/>
       <c r="H517" s="4"/>
       <c r="I517" s="4"/>
-      <c r="J517" s="6"/>
+      <c r="J517" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
     </row>
@@ -19079,7 +20222,9 @@
       <c r="G518" s="3"/>
       <c r="H518" s="4"/>
       <c r="I518" s="4"/>
-      <c r="J518" s="6"/>
+      <c r="J518" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K518" s="7"/>
       <c r="L518" s="7"/>
     </row>
@@ -19103,7 +20248,9 @@
       <c r="G519" s="3"/>
       <c r="H519" s="4"/>
       <c r="I519" s="4"/>
-      <c r="J519" s="6"/>
+      <c r="J519" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K519" s="7"/>
       <c r="L519" s="7"/>
     </row>
@@ -19133,7 +20280,9 @@
         <v>1621</v>
       </c>
       <c r="I520" s="4"/>
-      <c r="J520" s="6"/>
+      <c r="J520" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
     </row>
@@ -19163,7 +20312,9 @@
         <v>1626</v>
       </c>
       <c r="I521" s="4"/>
-      <c r="J521" s="6"/>
+      <c r="J521" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K521" s="7"/>
       <c r="L521" s="7"/>
     </row>
@@ -19193,7 +20344,9 @@
         <v>1630</v>
       </c>
       <c r="I522" s="4"/>
-      <c r="J522" s="6"/>
+      <c r="J522" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K522" s="7"/>
       <c r="L522" s="7"/>
     </row>
@@ -19217,7 +20370,9 @@
       <c r="G523" s="3"/>
       <c r="H523" s="4"/>
       <c r="I523" s="4"/>
-      <c r="J523" s="6"/>
+      <c r="J523" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K523" s="7"/>
       <c r="L523" s="7"/>
     </row>
@@ -19243,7 +20398,9 @@
       <c r="I524" s="9" t="s">
         <v>1401</v>
       </c>
-      <c r="J524" s="6"/>
+      <c r="J524" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K524" s="7"/>
       <c r="L524" s="7"/>
     </row>
@@ -19267,7 +20424,9 @@
       <c r="G525" s="3"/>
       <c r="H525" s="4"/>
       <c r="I525" s="4"/>
-      <c r="J525" s="6"/>
+      <c r="J525" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K525" s="7"/>
       <c r="L525" s="7"/>
     </row>
@@ -19291,7 +20450,9 @@
       <c r="G526" s="3"/>
       <c r="H526" s="4"/>
       <c r="I526" s="4"/>
-      <c r="J526" s="6"/>
+      <c r="J526" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K526" s="7"/>
       <c r="L526" s="7"/>
     </row>
@@ -19319,7 +20480,9 @@
       <c r="I527" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="J527" s="6"/>
+      <c r="J527" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K527" s="7"/>
       <c r="L527" s="7"/>
     </row>
@@ -19343,7 +20506,9 @@
       <c r="G528" s="3"/>
       <c r="H528" s="4"/>
       <c r="I528" s="4"/>
-      <c r="J528" s="6"/>
+      <c r="J528" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K528" s="7"/>
       <c r="L528" s="7"/>
     </row>
@@ -19367,7 +20532,9 @@
       <c r="G529" s="3"/>
       <c r="H529" s="4"/>
       <c r="I529" s="4"/>
-      <c r="J529" s="6"/>
+      <c r="J529" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K529" s="7"/>
       <c r="L529" s="7"/>
     </row>
@@ -19391,7 +20558,9 @@
       <c r="G530" s="3"/>
       <c r="H530" s="4"/>
       <c r="I530" s="4"/>
-      <c r="J530" s="6"/>
+      <c r="J530" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K530" s="7"/>
       <c r="L530" s="7"/>
     </row>
@@ -19417,7 +20586,9 @@
       <c r="I531" s="9" t="s">
         <v>1659</v>
       </c>
-      <c r="J531" s="6"/>
+      <c r="J531" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K531" s="7"/>
       <c r="L531" s="7"/>
     </row>
@@ -19441,7 +20612,9 @@
       <c r="G532" s="3"/>
       <c r="H532" s="4"/>
       <c r="I532" s="4"/>
-      <c r="J532" s="6"/>
+      <c r="J532" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K532" s="7"/>
       <c r="L532" s="7"/>
     </row>
@@ -19471,7 +20644,9 @@
         <v>1667</v>
       </c>
       <c r="I533" s="4"/>
-      <c r="J533" s="6"/>
+      <c r="J533" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K533" s="7"/>
       <c r="L533" s="7"/>
     </row>
@@ -19501,7 +20676,9 @@
         <v>1672</v>
       </c>
       <c r="I534" s="4"/>
-      <c r="J534" s="6"/>
+      <c r="J534" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K534" s="7"/>
       <c r="L534" s="7"/>
     </row>
@@ -19525,7 +20702,9 @@
       <c r="G535" s="3"/>
       <c r="H535" s="4"/>
       <c r="I535" s="4"/>
-      <c r="J535" s="6"/>
+      <c r="J535" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K535" s="7"/>
       <c r="L535" s="7"/>
     </row>
@@ -19549,7 +20728,9 @@
       <c r="G536" s="3"/>
       <c r="H536" s="4"/>
       <c r="I536" s="4"/>
-      <c r="J536" s="6"/>
+      <c r="J536" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K536" s="7"/>
       <c r="L536" s="7"/>
     </row>
@@ -19573,7 +20754,9 @@
       <c r="G537" s="3"/>
       <c r="H537" s="4"/>
       <c r="I537" s="4"/>
-      <c r="J537" s="6"/>
+      <c r="J537" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K537" s="7"/>
       <c r="L537" s="7"/>
     </row>
@@ -19597,7 +20780,9 @@
       <c r="G538" s="3"/>
       <c r="H538" s="4"/>
       <c r="I538" s="4"/>
-      <c r="J538" s="6"/>
+      <c r="J538" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K538" s="7"/>
       <c r="L538" s="7"/>
     </row>
@@ -19621,7 +20806,9 @@
       <c r="G539" s="3"/>
       <c r="H539" s="4"/>
       <c r="I539" s="4"/>
-      <c r="J539" s="6"/>
+      <c r="J539" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K539" s="7"/>
       <c r="L539" s="7"/>
     </row>
@@ -19645,7 +20832,9 @@
       <c r="G540" s="3"/>
       <c r="H540" s="4"/>
       <c r="I540" s="4"/>
-      <c r="J540" s="6"/>
+      <c r="J540" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K540" s="7"/>
       <c r="L540" s="7"/>
     </row>
@@ -19673,7 +20862,9 @@
         <v>1695</v>
       </c>
       <c r="I541" s="4"/>
-      <c r="J541" s="6"/>
+      <c r="J541" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K541" s="7"/>
       <c r="L541" s="7"/>
     </row>
@@ -19697,7 +20888,9 @@
       <c r="G542" s="3"/>
       <c r="H542" s="4"/>
       <c r="I542" s="4"/>
-      <c r="J542" s="6"/>
+      <c r="J542" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K542" s="7"/>
       <c r="L542" s="7"/>
     </row>
@@ -19727,7 +20920,9 @@
         <v>1703</v>
       </c>
       <c r="I543" s="4"/>
-      <c r="J543" s="6"/>
+      <c r="J543" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K543" s="7"/>
       <c r="L543" s="7"/>
     </row>
@@ -19757,7 +20952,9 @@
         <v>1707</v>
       </c>
       <c r="I544" s="4"/>
-      <c r="J544" s="6"/>
+      <c r="J544" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K544" s="7"/>
       <c r="L544" s="7"/>
     </row>
@@ -19783,7 +20980,9 @@
       <c r="G545" s="3"/>
       <c r="H545" s="4"/>
       <c r="I545" s="4"/>
-      <c r="J545" s="6"/>
+      <c r="J545" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K545" s="7"/>
       <c r="L545" s="7"/>
     </row>
@@ -19809,7 +21008,9 @@
       <c r="G546" s="3"/>
       <c r="H546" s="4"/>
       <c r="I546" s="4"/>
-      <c r="J546" s="6"/>
+      <c r="J546" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K546" s="7"/>
       <c r="L546" s="7"/>
     </row>
@@ -19833,7 +21034,9 @@
       <c r="G547" s="3"/>
       <c r="H547" s="4"/>
       <c r="I547" s="4"/>
-      <c r="J547" s="6"/>
+      <c r="J547" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K547" s="7"/>
       <c r="L547" s="7"/>
     </row>
@@ -19859,7 +21062,9 @@
       <c r="G548" s="3"/>
       <c r="H548" s="4"/>
       <c r="I548" s="4"/>
-      <c r="J548" s="6"/>
+      <c r="J548" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K548" s="7"/>
       <c r="L548" s="7"/>
     </row>
@@ -19885,7 +21090,9 @@
       <c r="G549" s="3"/>
       <c r="H549" s="4"/>
       <c r="I549" s="4"/>
-      <c r="J549" s="6"/>
+      <c r="J549" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K549" s="7"/>
       <c r="L549" s="7"/>
     </row>
@@ -19915,7 +21122,9 @@
         <v>1720</v>
       </c>
       <c r="I550" s="4"/>
-      <c r="J550" s="6"/>
+      <c r="J550" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K550" s="7"/>
       <c r="L550" s="7"/>
     </row>
@@ -19939,7 +21148,9 @@
       <c r="G551" s="3"/>
       <c r="H551" s="4"/>
       <c r="I551" s="4"/>
-      <c r="J551" s="6"/>
+      <c r="J551" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K551" s="7"/>
       <c r="L551" s="7"/>
     </row>
@@ -19965,8 +21176,12 @@
       <c r="I552" s="9" t="s">
         <v>1727</v>
       </c>
-      <c r="J552" s="6"/>
-      <c r="K552" s="7"/>
+      <c r="J552" s="6" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K552" s="7" t="s">
+        <v>1815</v>
+      </c>
       <c r="L552" s="7"/>
     </row>
     <row r="553" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -19991,7 +21206,9 @@
       <c r="I553" s="9" t="s">
         <v>1343</v>
       </c>
-      <c r="J553" s="6"/>
+      <c r="J553" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K553" s="7"/>
       <c r="L553" s="7"/>
     </row>
@@ -20017,7 +21234,9 @@
         <v>1734</v>
       </c>
       <c r="I554" s="4"/>
-      <c r="J554" s="6"/>
+      <c r="J554" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K554" s="7"/>
       <c r="L554" s="7"/>
     </row>
@@ -20041,7 +21260,9 @@
       <c r="G555" s="3"/>
       <c r="H555" s="4"/>
       <c r="I555" s="4"/>
-      <c r="J555" s="6"/>
+      <c r="J555" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K555" s="7"/>
       <c r="L555" s="7"/>
     </row>
@@ -20065,7 +21286,9 @@
       <c r="G556" s="3"/>
       <c r="H556" s="4"/>
       <c r="I556" s="4"/>
-      <c r="J556" s="6"/>
+      <c r="J556" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K556" s="7"/>
       <c r="L556" s="7"/>
     </row>
@@ -20091,7 +21314,9 @@
       <c r="G557" s="3"/>
       <c r="H557" s="4"/>
       <c r="I557" s="4"/>
-      <c r="J557" s="6"/>
+      <c r="J557" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K557" s="7"/>
       <c r="L557" s="7"/>
     </row>
@@ -20117,7 +21342,9 @@
       <c r="G558" s="3"/>
       <c r="H558" s="4"/>
       <c r="I558" s="4"/>
-      <c r="J558" s="6"/>
+      <c r="J558" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K558" s="7"/>
       <c r="L558" s="7"/>
     </row>
@@ -20143,7 +21370,9 @@
       <c r="G559" s="3"/>
       <c r="H559" s="4"/>
       <c r="I559" s="4"/>
-      <c r="J559" s="6"/>
+      <c r="J559" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K559" s="7"/>
       <c r="L559" s="7"/>
     </row>
@@ -20171,7 +21400,9 @@
       <c r="I560" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="J560" s="6"/>
+      <c r="J560" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K560" s="7"/>
       <c r="L560" s="7"/>
     </row>
@@ -20197,7 +21428,9 @@
       <c r="G561" s="3"/>
       <c r="H561" s="4"/>
       <c r="I561" s="4"/>
-      <c r="J561" s="6"/>
+      <c r="J561" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K561" s="7"/>
       <c r="L561" s="7"/>
     </row>
@@ -20223,7 +21456,9 @@
       <c r="G562" s="3"/>
       <c r="H562" s="4"/>
       <c r="I562" s="4"/>
-      <c r="J562" s="6"/>
+      <c r="J562" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K562" s="7"/>
       <c r="L562" s="7"/>
     </row>
@@ -20249,7 +21484,9 @@
       <c r="G563" s="3"/>
       <c r="H563" s="4"/>
       <c r="I563" s="4"/>
-      <c r="J563" s="6"/>
+      <c r="J563" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K563" s="7"/>
       <c r="L563" s="7"/>
     </row>
@@ -20275,7 +21512,9 @@
       <c r="G564" s="3"/>
       <c r="H564" s="4"/>
       <c r="I564" s="4"/>
-      <c r="J564" s="6"/>
+      <c r="J564" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K564" s="7"/>
       <c r="L564" s="7"/>
     </row>
@@ -20301,7 +21540,9 @@
         <v>1768</v>
       </c>
       <c r="I565" s="4"/>
-      <c r="J565" s="6"/>
+      <c r="J565" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K565" s="7"/>
       <c r="L565" s="7"/>
     </row>
@@ -20327,7 +21568,9 @@
       <c r="G566" s="3"/>
       <c r="H566" s="4"/>
       <c r="I566" s="4"/>
-      <c r="J566" s="6"/>
+      <c r="J566" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K566" s="7"/>
       <c r="L566" s="7"/>
     </row>
@@ -20351,7 +21594,9 @@
       <c r="G567" s="3"/>
       <c r="H567" s="4"/>
       <c r="I567" s="4"/>
-      <c r="J567" s="6"/>
+      <c r="J567" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K567" s="7"/>
       <c r="L567" s="7"/>
     </row>
@@ -20379,7 +21624,9 @@
         <v>1779</v>
       </c>
       <c r="I568" s="4"/>
-      <c r="J568" s="6"/>
+      <c r="J568" s="6" t="s">
+        <v>1796</v>
+      </c>
       <c r="K568" s="7"/>
       <c r="L568" s="7"/>
     </row>
